--- a/Notebooks/trades_taken.xlsx
+++ b/Notebooks/trades_taken.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R121"/>
+  <dimension ref="A1:R119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,19 +522,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83.57546997070312</v>
+        <v>184.7147064208984</v>
       </c>
       <c r="B2" t="n">
-        <v>2.348797082901001</v>
+        <v>331.4285583496094</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4257500556311</v>
+        <v>5.21881250732129</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8539033174843764</v>
+        <v>5.803412276142656</v>
       </c>
       <c r="E2" t="n">
-        <v>3.679534870230139</v>
+        <v>1.106100513230704</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -562,19 +562,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83.94680023193359</v>
+        <v>185.5836486816406</v>
       </c>
       <c r="B3" t="n">
-        <v>2.306900978088379</v>
+        <v>335.5332641601562</v>
       </c>
       <c r="C3" t="n">
-        <v>4.43018326763257</v>
+        <v>5.223505716695444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8359050558986779</v>
+        <v>5.815721099515246</v>
       </c>
       <c r="E3" t="n">
-        <v>3.699696532784575</v>
+        <v>1.1020708121672</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -592,16 +592,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004443053223160298</v>
+        <v>0.004704239730442428</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01783726023743015</v>
+        <v>0.01238488871021493</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -612,19 +612,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81.62861633300781</v>
+        <v>182.9169006347656</v>
       </c>
       <c r="B4" t="n">
-        <v>2.16712498664856</v>
+        <v>335.4034118652344</v>
       </c>
       <c r="C4" t="n">
-        <v>4.402179890848059</v>
+        <v>5.209031954817122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7734013981630147</v>
+        <v>5.815334021863411</v>
       </c>
       <c r="E4" t="n">
-        <v>3.726314302903278</v>
+        <v>1.087871361129742</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02761491673918426</v>
+        <v>-0.01436952051443752</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06059037330490236</v>
+        <v>-0.0003870027469463633</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -662,19 +662,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81.24733734130859</v>
+        <v>186.8221282958984</v>
       </c>
       <c r="B5" t="n">
-        <v>2.122097015380859</v>
+        <v>332.3473815917969</v>
       </c>
       <c r="C5" t="n">
-        <v>4.397498049488965</v>
+        <v>5.230156978607081</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7524047579878383</v>
+        <v>5.806180751990471</v>
       </c>
       <c r="E5" t="n">
-        <v>3.739981156789069</v>
+        <v>1.115483045008688</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -692,19 +692,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004670898623881814</v>
+        <v>0.02134973667048112</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02077774542082855</v>
+        <v>-0.0091115062200543</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>100</v>
@@ -712,19 +712,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81.36936187744141</v>
+        <v>186.0031280517578</v>
       </c>
       <c r="B6" t="n">
-        <v>2.091640949249268</v>
+        <v>329.5710144042969</v>
       </c>
       <c r="C6" t="n">
-        <v>4.398998812444086</v>
+        <v>5.225763491054358</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7379489010945185</v>
+        <v>5.797791852433679</v>
       </c>
       <c r="E6" t="n">
-        <v>3.754114708153488</v>
+        <v>1.11703453020351</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001501889663413802</v>
+        <v>-0.004383850305160086</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01435187265749283</v>
+        <v>-0.008353810925792238</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>100</v>
@@ -762,19 +762,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>76.05021667480469</v>
+        <v>177.8530883789062</v>
       </c>
       <c r="B7" t="n">
-        <v>2.052545070648193</v>
+        <v>321.5814208984375</v>
       </c>
       <c r="C7" t="n">
-        <v>4.331393867811101</v>
+        <v>5.180957863320478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7190805210062488</v>
+        <v>5.773250764797821</v>
       </c>
       <c r="E7" t="n">
-        <v>3.702998599501681</v>
+        <v>1.089620468097828</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06537036889447922</v>
+        <v>-0.04381668070971212</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01869148651689312</v>
+        <v>-0.02424240347805051</v>
       </c>
       <c r="O7" t="n">
         <v>-0</v>
@@ -812,19 +812,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78.12391662597656</v>
+        <v>183.0966949462891</v>
       </c>
       <c r="B8" t="n">
-        <v>2.163798093795776</v>
+        <v>327.953125</v>
       </c>
       <c r="C8" t="n">
-        <v>4.358296240772916</v>
+        <v>5.210014400978443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7718650543188158</v>
+        <v>5.792870686585944</v>
       </c>
       <c r="E8" t="n">
-        <v>3.683773244059559</v>
+        <v>1.104772929357007</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02726750878355988</v>
+        <v>0.02948279737606585</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0542024751312522</v>
+        <v>0.01981365740521079</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -862,19 +862,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>76.74135589599609</v>
+        <v>184.6148223876953</v>
       </c>
       <c r="B9" t="n">
-        <v>2.139741897583008</v>
+        <v>330.1103210449219</v>
       </c>
       <c r="C9" t="n">
-        <v>4.340440753362171</v>
+        <v>5.218271613469879</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7606852131538863</v>
+        <v>5.799426904789393</v>
       </c>
       <c r="E9" t="n">
-        <v>3.675687676822235</v>
+        <v>1.108383937863929</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -892,19 +892,19 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01769702275168272</v>
+        <v>0.008291397296120495</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01111757898379917</v>
+        <v>0.00657775724784404</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>100</v>
@@ -912,19 +912,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72.12104034423828</v>
+        <v>187.4413757324219</v>
       </c>
       <c r="B10" t="n">
-        <v>2.078129053115845</v>
+        <v>327.5036926269531</v>
       </c>
       <c r="C10" t="n">
-        <v>4.278345823414633</v>
+        <v>5.233466133760857</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7314679952317142</v>
+        <v>5.791499330208546</v>
       </c>
       <c r="E10" t="n">
-        <v>3.639125299849106</v>
+        <v>1.129196503110411</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -942,19 +942,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06020633200721015</v>
+        <v>0.01531054391066577</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02879452168355412</v>
+        <v>-0.007896234233809474</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>100</v>
@@ -962,19 +962,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75.26462554931641</v>
+        <v>186.2428436279297</v>
       </c>
       <c r="B11" t="n">
-        <v>2.068217992782593</v>
+        <v>332.8267822265625</v>
       </c>
       <c r="C11" t="n">
-        <v>4.321010244202987</v>
+        <v>5.227051433047265</v>
       </c>
       <c r="D11" t="n">
-        <v>0.726687363461382</v>
+        <v>5.807622181149471</v>
       </c>
       <c r="E11" t="n">
-        <v>3.685967453584255</v>
+        <v>1.111355999905367</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04358762976897723</v>
+        <v>-0.006394170442939551</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.004769222738304824</v>
+        <v>0.01625352543939917</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1012,19 +1012,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67.06245422363281</v>
+        <v>188.2903442382812</v>
       </c>
       <c r="B12" t="n">
-        <v>1.88958203792572</v>
+        <v>334.1150817871094</v>
       </c>
       <c r="C12" t="n">
-        <v>4.20562433779807</v>
+        <v>5.237985155741204</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6363556606609757</v>
+        <v>5.811485489879658</v>
       </c>
       <c r="E12" t="n">
-        <v>3.649521266668159</v>
+        <v>1.119551906398167</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1042,19 +1042,19 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1089777736329692</v>
+        <v>0.01099371428435658</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08637191798942556</v>
+        <v>0.003870780926728212</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>100</v>
@@ -1062,19 +1062,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68.42014312744141</v>
+        <v>191.2866821289062</v>
       </c>
       <c r="B13" t="n">
-        <v>1.945557951927185</v>
+        <v>335.5732116699219</v>
       </c>
       <c r="C13" t="n">
-        <v>4.225667271442059</v>
+        <v>5.253773256296206</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6655488006766401</v>
+        <v>5.81584014920781</v>
       </c>
       <c r="E13" t="n">
-        <v>3.644052688712213</v>
+        <v>1.132253984661991</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02024514192816618</v>
+        <v>0.01591339111278667</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0296234367590158</v>
+        <v>0.004364154635023487</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68.12567138671875</v>
+        <v>192.2754821777344</v>
       </c>
       <c r="B14" t="n">
-        <v>1.921674013137817</v>
+        <v>337.8102722167969</v>
       </c>
       <c r="C14" t="n">
-        <v>4.221354108152735</v>
+        <v>5.25892914669051</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6531966880141138</v>
+        <v>5.822484413078896</v>
       </c>
       <c r="E14" t="n">
-        <v>3.650533878661515</v>
+        <v>1.13270127562991</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -1142,19 +1142,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.004303874959369236</v>
+        <v>0.005169204870006494</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0122761384546316</v>
+        <v>0.006666385960138577</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>100</v>
@@ -1162,19 +1162,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68.04029846191406</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="B15" t="n">
-        <v>1.919531941413879</v>
+        <v>337.5606079101562</v>
       </c>
       <c r="C15" t="n">
-        <v>4.220100154083503</v>
+        <v>5.251734911452216</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6520813758067862</v>
+        <v>5.821745073183263</v>
       </c>
       <c r="E15" t="n">
-        <v>3.650254581662386</v>
+        <v>1.126030989391238</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.001253168197346111</v>
+        <v>-0.007168418675203125</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.001114690477829972</v>
+        <v>-0.0007390666512366861</v>
       </c>
       <c r="O15" t="n">
         <v>-0</v>
@@ -1212,19 +1212,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69.73886108398438</v>
+        <v>185.3838806152344</v>
       </c>
       <c r="B16" t="n">
-        <v>1.903496980667114</v>
+        <v>343.2432250976562</v>
       </c>
       <c r="C16" t="n">
-        <v>4.244757710227782</v>
+        <v>5.222428705529022</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6436927106385341</v>
+        <v>5.838439306937361</v>
       </c>
       <c r="E16" t="n">
-        <v>3.682242884983331</v>
+        <v>1.08489405834881</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1242,16 +1242,16 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02496406777258753</v>
+        <v>-0.02888094347234282</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.008353578495262859</v>
+        <v>0.01683436116163306</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1262,19 +1262,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69.96452331542969</v>
+        <v>180.1203002929688</v>
       </c>
       <c r="B17" t="n">
-        <v>1.913934946060181</v>
+        <v>339.2683715820312</v>
       </c>
       <c r="C17" t="n">
-        <v>4.247988303798298</v>
+        <v>5.193624962614797</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6491613039788364</v>
+        <v>5.826791450769824</v>
       </c>
       <c r="E17" t="n">
-        <v>3.680694544791956</v>
+        <v>1.064344817352811</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1292,19 +1292,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.003235817561940912</v>
+        <v>-0.0283928694598331</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005483573391016572</v>
+        <v>-0.01158028250810805</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R17" t="n">
         <v>100</v>
@@ -1312,19 +1312,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>69.38337707519531</v>
+        <v>173.9778137207031</v>
       </c>
       <c r="B18" t="n">
-        <v>1.90872597694397</v>
+        <v>332.6070556640625</v>
       </c>
       <c r="C18" t="n">
-        <v>4.239647315410274</v>
+        <v>5.158927783732494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6464359917185083</v>
+        <v>5.806961780196065</v>
       </c>
       <c r="E18" t="n">
-        <v>3.674735171924068</v>
+        <v>1.043700357823711</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.008306298859699579</v>
+        <v>-0.03410213375324578</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.002721601968203591</v>
+        <v>-0.01963435579599293</v>
       </c>
       <c r="O18" t="n">
         <v>-0</v>
@@ -1362,19 +1362,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66.10388946533203</v>
+        <v>171.6706237792969</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805065035820007</v>
+        <v>330.8193664550781</v>
       </c>
       <c r="C19" t="n">
-        <v>4.191227587264665</v>
+        <v>5.145577662871488</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5905966220609579</v>
+        <v>5.801572505737814</v>
       </c>
       <c r="E19" t="n">
-        <v>3.675112754584602</v>
+        <v>1.034169461351605</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.04726618605360022</v>
+        <v>-0.01326140323334624</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05430896963530207</v>
+        <v>-0.005374778371478595</v>
       </c>
       <c r="O19" t="n">
         <v>-0</v>
@@ -1412,19 +1412,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>65.34912872314453</v>
+        <v>185.1841430664062</v>
       </c>
       <c r="B20" t="n">
-        <v>1.732426047325134</v>
+        <v>322.4402770996094</v>
       </c>
       <c r="C20" t="n">
-        <v>4.179744107512256</v>
+        <v>5.221350697954668</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5495227656442502</v>
+        <v>5.775917931798511</v>
       </c>
       <c r="E20" t="n">
-        <v>3.699523192508286</v>
+        <v>1.12812315790135</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1442,19 +1442,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.01141779626421724</v>
+        <v>0.07871771529462501</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.04024175697463139</v>
+        <v>-0.02532829152433114</v>
       </c>
       <c r="O20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>100</v>
@@ -1462,34 +1462,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>59.99173355102539</v>
+        <v>189.8084869384766</v>
       </c>
       <c r="B21" t="n">
-        <v>1.62054705619812</v>
+        <v>323.8984069824219</v>
       </c>
       <c r="C21" t="n">
-        <v>4.094206778580794</v>
+        <v>5.246015600341975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4827637812513766</v>
+        <v>5.780429907926294</v>
       </c>
       <c r="E21" t="n">
-        <v>3.672325686008559</v>
+        <v>1.149590552089203</v>
       </c>
       <c r="F21" t="n">
-        <v>3.683309524759123</v>
+        <v>1.104362533051159</v>
       </c>
       <c r="G21" t="n">
-        <v>0.03090251769028243</v>
+        <v>0.02986159584211987</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3554350768649018</v>
+        <v>1.514588144490569</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1498,19 +1498,19 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08198112624907461</v>
+        <v>0.02497159743538102</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0645793748597554</v>
+        <v>0.004522170418437055</v>
       </c>
       <c r="O21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>100</v>
@@ -1518,140 +1518,140 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>59.26666641235352</v>
+        <v>188.3103179931641</v>
       </c>
       <c r="B22" t="n">
-        <v>1.574198961257935</v>
+        <v>318.1658325195312</v>
       </c>
       <c r="C22" t="n">
-        <v>4.082047030120696</v>
+        <v>5.238091229664618</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4537465468720594</v>
+        <v>5.762572732764129</v>
       </c>
       <c r="E22" t="n">
-        <v>3.685523727463104</v>
+        <v>1.154321049785048</v>
       </c>
       <c r="F22" t="n">
-        <v>3.683608967620772</v>
+        <v>1.106773559878876</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03089303085148003</v>
+        <v>0.0318872644354834</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06198031690505453</v>
+        <v>1.491112227653569</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0120861174657535</v>
+        <v>-0.007893055623999112</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.02860027714895264</v>
+        <v>-0.01769868063352886</v>
       </c>
       <c r="O22" t="n">
-        <v>-0</v>
+        <v>0.00817083340177689</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>-0.01797645841130664</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0</v>
+        <v>-0.009805625009529749</v>
       </c>
       <c r="R22" t="n">
-        <v>100</v>
+        <v>99.01943749904703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58.79404449462891</v>
+        <v>189.8184967041016</v>
       </c>
       <c r="B23" t="n">
-        <v>1.510475993156433</v>
+        <v>310.5557556152344</v>
       </c>
       <c r="C23" t="n">
-        <v>4.07404056567005</v>
+        <v>5.246068335084544</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4124248284090762</v>
+        <v>5.738363452452096</v>
       </c>
       <c r="E23" t="n">
-        <v>3.713627784159959</v>
+        <v>1.1794545784901</v>
       </c>
       <c r="F23" t="n">
-        <v>3.68430553018954</v>
+        <v>1.110642748195021</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03142729567370661</v>
+        <v>0.035747769379214</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9330186814308152</v>
+        <v>1.924926547587341</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.007974498083565207</v>
+        <v>0.008009007297158588</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.04047961513745424</v>
+        <v>-0.02391858624175092</v>
       </c>
       <c r="O23" t="n">
-        <v>-0</v>
+        <v>-0.007929642217793508</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>-0.02391858624175092</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0</v>
+        <v>-0.03184822845954442</v>
       </c>
       <c r="R23" t="n">
-        <v>100</v>
+        <v>95.8658438316418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>50.68783187866211</v>
+        <v>186.7122802734375</v>
       </c>
       <c r="B24" t="n">
-        <v>1.213521003723145</v>
+        <v>308.5982971191406</v>
       </c>
       <c r="C24" t="n">
-        <v>3.925685879398702</v>
+        <v>5.229568823818084</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1935260544180389</v>
+        <v>5.732040421829392</v>
       </c>
       <c r="E24" t="n">
-        <v>3.756565936167991</v>
+        <v>1.167436017851239</v>
       </c>
       <c r="F24" t="n">
-        <v>3.685818111852776</v>
+        <v>1.114620981031096</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03416438171037033</v>
+        <v>0.03746617420077004</v>
       </c>
       <c r="H24" t="n">
-        <v>2.070806517588454</v>
+        <v>1.409672536542503</v>
       </c>
       <c r="I24" t="n">
         <v>-1</v>
@@ -1660,60 +1660,60 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1378747232928895</v>
+        <v>-0.01636413987360874</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1965969606790926</v>
+        <v>-0.006303082331273746</v>
       </c>
       <c r="O24" t="n">
-        <v>-0</v>
+        <v>0.01644350495297382</v>
       </c>
       <c r="P24" t="n">
-        <v>-0</v>
+        <v>-0.006303082331273746</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0</v>
+        <v>0.01014042262170007</v>
       </c>
       <c r="R24" t="n">
-        <v>100</v>
+        <v>96.83796400308054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55.06094741821289</v>
+        <v>182.5872955322266</v>
       </c>
       <c r="B25" t="n">
-        <v>1.47152304649353</v>
+        <v>305.3225708007812</v>
       </c>
       <c r="C25" t="n">
-        <v>4.008440706580823</v>
+        <v>5.207228390341847</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3862979504739634</v>
+        <v>5.721368826915722</v>
       </c>
       <c r="E25" t="n">
-        <v>3.670859869464314</v>
+        <v>1.152658237915567</v>
       </c>
       <c r="F25" t="n">
-        <v>3.682362047486539</v>
+        <v>1.11647974067644</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03181204715189665</v>
+        <v>0.03842118383900175</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3615667349952145</v>
+        <v>0.9416289042713365</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
@@ -1722,3464 +1722,3464 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08627545068448117</v>
+        <v>-0.02209273399248279</v>
       </c>
       <c r="N25" t="n">
-        <v>0.212606161721818</v>
+        <v>-0.01061485545752938</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.08599767290670339</v>
+        <v>0.02217209907184787</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2123283839440402</v>
+        <v>-0.01061485545752938</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1263307110373368</v>
+        <v>0.01155724361431849</v>
       </c>
       <c r="R25" t="n">
-        <v>112.6330711037337</v>
+        <v>97.95714394417875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54.39728546142578</v>
+        <v>184.7446746826172</v>
       </c>
       <c r="B26" t="n">
-        <v>1.436115980148315</v>
+        <v>301.6273498535156</v>
       </c>
       <c r="C26" t="n">
-        <v>3.996314253010727</v>
+        <v>5.218974734961551</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3619422334846218</v>
+        <v>5.70919231456057</v>
       </c>
       <c r="E26" t="n">
-        <v>3.680017565395262</v>
+        <v>1.173033727945996</v>
       </c>
       <c r="F26" t="n">
-        <v>3.678657190348627</v>
+        <v>1.119279700563564</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02696064723877405</v>
+        <v>0.04045062627938346</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05045780372357724</v>
+        <v>1.328879978548778</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.01205322443412193</v>
+        <v>0.01181560384090274</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.02406150989587674</v>
+        <v>-0.01210267861158787</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0001984126984126984</v>
+        <v>-0.01173623876153766</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0002777777777777778</v>
+        <v>-0.01210267861158787</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.936507936507937e-05</v>
+        <v>-0.02383891737312553</v>
       </c>
       <c r="R26" t="n">
-        <v>112.642010236361</v>
+        <v>95.62195168358613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>53.32602691650391</v>
+        <v>187.7509918212891</v>
       </c>
       <c r="B27" t="n">
-        <v>1.399487018585205</v>
+        <v>302.9356689453125</v>
       </c>
       <c r="C27" t="n">
-        <v>3.97642452186545</v>
+        <v>5.235116573300273</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3361057541784433</v>
+        <v>5.713520469255783</v>
       </c>
       <c r="E27" t="n">
-        <v>3.68270600299673</v>
+        <v>1.186108327067464</v>
       </c>
       <c r="F27" t="n">
-        <v>3.67764256052338</v>
+        <v>1.124104093512046</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02637178785807618</v>
+        <v>0.04243242929709501</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1920022449975844</v>
+        <v>1.461246376475134</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.01969323534869261</v>
+        <v>0.01627282163254007</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.02550557341429172</v>
+        <v>0.004337534684544453</v>
       </c>
       <c r="O27" t="n">
-        <v>-0</v>
+        <v>-0.01619345655317499</v>
       </c>
       <c r="P27" t="n">
-        <v>-0</v>
+        <v>0.004337534684544453</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0</v>
+        <v>-0.01185592186863054</v>
       </c>
       <c r="R27" t="n">
-        <v>112.642010236361</v>
+        <v>94.48826529549957</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52.23699951171875</v>
+        <v>187.6710968017578</v>
       </c>
       <c r="B28" t="n">
-        <v>1.368018984794617</v>
+        <v>302.456298828125</v>
       </c>
       <c r="C28" t="n">
-        <v>3.955791046712941</v>
+        <v>5.234690945596637</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3133636968779059</v>
+        <v>5.711936800350696</v>
       </c>
       <c r="E28" t="n">
-        <v>3.681946520786321</v>
+        <v>1.186805000139769</v>
       </c>
       <c r="F28" t="n">
-        <v>3.677551224359718</v>
+        <v>1.128205697051184</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02635259364966654</v>
+        <v>0.04438524933822412</v>
       </c>
       <c r="H28" t="n">
-        <v>0.166788001402609</v>
+        <v>1.320242737447447</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02042206156649018</v>
+        <v>-0.0004255371370144312</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.02248540598997528</v>
+        <v>-0.001582415563200157</v>
       </c>
       <c r="O28" t="n">
-        <v>-0</v>
+        <v>0.0005049022163795106</v>
       </c>
       <c r="P28" t="n">
-        <v>-0</v>
+        <v>-0.001582415563200157</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0</v>
+        <v>-0.001077513346820646</v>
       </c>
       <c r="R28" t="n">
-        <v>112.642010236361</v>
+        <v>94.38645292852574</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>53.09817886352539</v>
+        <v>189.5887756347656</v>
       </c>
       <c r="B29" t="n">
-        <v>1.362069964408875</v>
+        <v>314.5705261230469</v>
       </c>
       <c r="C29" t="n">
-        <v>3.972142631304306</v>
+        <v>5.24485738782994</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3090055752838107</v>
+        <v>5.751208299404545</v>
       </c>
       <c r="E29" t="n">
-        <v>3.702106612086523</v>
+        <v>1.169140856245554</v>
       </c>
       <c r="F29" t="n">
-        <v>3.678872171122932</v>
+        <v>1.131243542970266</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02691049579936853</v>
+        <v>0.04503166826154525</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8633969859498525</v>
+        <v>0.8415702712850818</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01648600340479822</v>
+        <v>0.01021829608122071</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.004348638762959323</v>
+        <v>0.04005281867780153</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-0.01013893100185563</v>
       </c>
       <c r="P29" t="n">
-        <v>-0</v>
+        <v>0.04005281867780153</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.0299138876759459</v>
       </c>
       <c r="R29" t="n">
-        <v>112.642010236361</v>
+        <v>97.20991867956063</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55.08050918579102</v>
+        <v>191.316650390625</v>
       </c>
       <c r="B30" t="n">
-        <v>1.407462954521179</v>
+        <v>311.0850524902344</v>
       </c>
       <c r="C30" t="n">
-        <v>4.008795918294685</v>
+        <v>5.253929910769562</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3417887606293291</v>
+        <v>5.740066355466205</v>
       </c>
       <c r="E30" t="n">
-        <v>3.710111092789664</v>
+        <v>1.186109355602546</v>
       </c>
       <c r="F30" t="n">
-        <v>3.68242146076996</v>
+        <v>1.134089185594872</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02606008059330441</v>
+        <v>0.04666413317054702</v>
       </c>
       <c r="H30" t="n">
-        <v>1.062530559741171</v>
+        <v>1.1147784491689</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.03733330153112546</v>
+        <v>0.009113803019584088</v>
       </c>
       <c r="N30" t="n">
-        <v>0.03332647462937399</v>
+        <v>-0.01108010237249346</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>-0.009034437940219008</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-0.01108010237249346</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>-0.02011454031271247</v>
       </c>
       <c r="R30" t="n">
-        <v>112.642010236361</v>
+        <v>95.2545858514851</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>53.8973274230957</v>
+        <v>192.6150817871094</v>
       </c>
       <c r="B31" t="n">
-        <v>1.474403977394104</v>
+        <v>310.495849609375</v>
       </c>
       <c r="C31" t="n">
-        <v>3.987080892698532</v>
+        <v>5.260693802565692</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3882538250055568</v>
+        <v>5.738170534486693</v>
       </c>
       <c r="E31" t="n">
-        <v>3.647790841849825</v>
+        <v>1.194216761405623</v>
       </c>
       <c r="F31" t="n">
-        <v>3.680512630183239</v>
+        <v>1.138232223669885</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02716156458910802</v>
+        <v>0.0481928786604718</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.204709258410533</v>
+        <v>1.161676564916566</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.02148095179556786</v>
+        <v>0.006786818574511244</v>
       </c>
       <c r="N31" t="n">
-        <v>0.04756148121546699</v>
+        <v>-0.001894025046021319</v>
       </c>
       <c r="O31" t="n">
-        <v>-0</v>
+        <v>-0.006707453495146165</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>-0.001894025046021319</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>-0.008601478541167485</v>
       </c>
       <c r="R31" t="n">
-        <v>112.642010236361</v>
+        <v>94.43525557533576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53.29018783569336</v>
+        <v>195.3217620849609</v>
       </c>
       <c r="B32" t="n">
-        <v>1.42160701751709</v>
+        <v>312.4932250976562</v>
       </c>
       <c r="C32" t="n">
-        <v>3.975752221085616</v>
+        <v>5.274648260681339</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3517879341974783</v>
+        <v>5.744582789253949</v>
       </c>
       <c r="E32" t="n">
-        <v>3.668329245716047</v>
+        <v>1.203627038298979</v>
       </c>
       <c r="F32" t="n">
-        <v>3.681453029135633</v>
+        <v>1.142435980264926</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02634542252100547</v>
+        <v>0.0501065252893487</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4981428333184859</v>
+        <v>1.221219345797685</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.01126474384594767</v>
+        <v>0.01405227603538939</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.03580901888933363</v>
+        <v>0.006432857285513016</v>
       </c>
       <c r="O32" t="n">
-        <v>-0</v>
+        <v>-0.01397291095602431</v>
       </c>
       <c r="P32" t="n">
-        <v>-0</v>
+        <v>0.006432857285513016</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0</v>
+        <v>-0.007540053670511292</v>
       </c>
       <c r="R32" t="n">
-        <v>112.642010236361</v>
+        <v>93.72320867990929</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>52.66159057617188</v>
+        <v>184.6647644042969</v>
       </c>
       <c r="B33" t="n">
-        <v>1.4063800573349</v>
+        <v>306.9804382324219</v>
       </c>
       <c r="C33" t="n">
-        <v>3.963886358248774</v>
+        <v>5.218542096966353</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3410190679100281</v>
+        <v>5.726784026444416</v>
       </c>
       <c r="E33" t="n">
-        <v>3.665874157364684</v>
+        <v>1.160134347796584</v>
       </c>
       <c r="F33" t="n">
-        <v>3.682544102568257</v>
+        <v>1.143829998421655</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02513924529449203</v>
+        <v>0.05019609289747783</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6631044412150464</v>
+        <v>0.3248131165951295</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.01179574111203363</v>
+        <v>-0.05456124072866231</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.0107110896292455</v>
+        <v>-0.01764130042663037</v>
       </c>
       <c r="O33" t="n">
-        <v>-0</v>
+        <v>0.05464060580802739</v>
       </c>
       <c r="P33" t="n">
-        <v>-0</v>
+        <v>-0.01764130042663037</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0</v>
+        <v>0.03699930538139702</v>
       </c>
       <c r="R33" t="n">
-        <v>112.642010236361</v>
+        <v>97.19090229918166</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>55.21048355102539</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="B34" t="n">
-        <v>1.429414033889771</v>
+        <v>311.354736328125</v>
       </c>
       <c r="C34" t="n">
-        <v>4.011152854653277</v>
+        <v>5.176003685815329</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3572645937839278</v>
+        <v>5.740932893433766</v>
       </c>
       <c r="E34" t="n">
-        <v>3.698943896532499</v>
+        <v>1.107569040019739</v>
       </c>
       <c r="F34" t="n">
-        <v>3.684964603461805</v>
+        <v>1.142573386641147</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02420827798996886</v>
+        <v>0.05080029748730964</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5774592094690284</v>
+        <v>-0.6890579062091517</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.04840136704884923</v>
+        <v>-0.04164634665296119</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0163782019197003</v>
+        <v>0.01424943596044792</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>0.04172571173232627</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.01424943596044792</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>0.05597514769277419</v>
       </c>
       <c r="R34" t="n">
-        <v>112.642010236361</v>
+        <v>102.6311774097723</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51.25557327270508</v>
+        <v>182.2577056884766</v>
       </c>
       <c r="B35" t="n">
-        <v>1.351645946502686</v>
+        <v>306.1215209960938</v>
       </c>
       <c r="C35" t="n">
-        <v>3.936824358890504</v>
+        <v>5.205421650864513</v>
       </c>
       <c r="D35" t="n">
-        <v>0.301323069437272</v>
+        <v>5.723982150556365</v>
       </c>
       <c r="E35" t="n">
-        <v>3.673501983251842</v>
+        <v>1.14899951085405</v>
       </c>
       <c r="F35" t="n">
-        <v>3.686126973541278</v>
+        <v>1.143721812714287</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02298095058530597</v>
+        <v>0.05066608997196639</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5493676270079466</v>
+        <v>0.1041662804981074</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.07163332077439954</v>
+        <v>0.02985494790647292</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.05440557147424929</v>
+        <v>-0.01680788734338112</v>
       </c>
       <c r="O35" t="n">
-        <v>-0</v>
+        <v>0.02937875743028244</v>
       </c>
       <c r="P35" t="n">
-        <v>-0</v>
+        <v>0.01736344289893668</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0</v>
+        <v>0.04674220032921912</v>
       </c>
       <c r="R35" t="n">
-        <v>112.642010236361</v>
+        <v>107.4283844642835</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51.16326141357422</v>
+        <v>179.8306579589844</v>
       </c>
       <c r="B36" t="n">
-        <v>1.348894000053406</v>
+        <v>303.1853332519531</v>
       </c>
       <c r="C36" t="n">
-        <v>3.935021723966745</v>
+        <v>5.19201561895362</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2992849974543997</v>
+        <v>5.714344279418622</v>
       </c>
       <c r="E36" t="n">
-        <v>3.673480393361425</v>
+        <v>1.142423562063159</v>
       </c>
       <c r="F36" t="n">
-        <v>3.685688848960183</v>
+        <v>1.146598287900005</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0231418605557224</v>
+        <v>0.04874719930907108</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5275485767171476</v>
+        <v>-0.08564032182397056</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.001801011153259702</v>
+        <v>-0.01331657128198804</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.002035996524385908</v>
+        <v>-0.009591575706884403</v>
       </c>
       <c r="O36" t="n">
-        <v>-0</v>
+        <v>0.01379276175817852</v>
       </c>
       <c r="P36" t="n">
-        <v>-0</v>
+        <v>-0.01014713126243996</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0</v>
+        <v>0.003645630495738562</v>
       </c>
       <c r="R36" t="n">
-        <v>112.642010236361</v>
+        <v>107.8200286587944</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56.67714691162109</v>
+        <v>182.8170166015625</v>
       </c>
       <c r="B37" t="n">
-        <v>1.433745980262756</v>
+        <v>302.7359619140625</v>
       </c>
       <c r="C37" t="n">
-        <v>4.037371076781038</v>
+        <v>5.208485743317564</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3602905858046841</v>
+        <v>5.712861012783621</v>
       </c>
       <c r="E37" t="n">
-        <v>3.722517742943999</v>
+        <v>1.159944834991074</v>
       </c>
       <c r="F37" t="n">
-        <v>3.687780008867785</v>
+        <v>1.151378288781918</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02451565971330489</v>
+        <v>0.04478311953043168</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4169610152225</v>
+        <v>0.1912896265150692</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1077704068447829</v>
+        <v>0.01660650456641966</v>
       </c>
       <c r="N37" t="n">
-        <v>0.06290485405524171</v>
+        <v>-0.001482167138728951</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.01613031409022918</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.002037722694284507</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>0.01816803678451369</v>
       </c>
       <c r="R37" t="n">
-        <v>112.642010236361</v>
+        <v>109.7789069055747</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>55.61968231201172</v>
+        <v>183.1166381835938</v>
       </c>
       <c r="B38" t="n">
-        <v>1.402017951011658</v>
+        <v>300.4888610839844</v>
       </c>
       <c r="C38" t="n">
-        <v>4.018537137031357</v>
+        <v>5.210123316932725</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3379125923903852</v>
+        <v>5.705410685348077</v>
       </c>
       <c r="E38" t="n">
-        <v>3.723239645363603</v>
+        <v>1.166862242184495</v>
       </c>
       <c r="F38" t="n">
-        <v>3.690205232539762</v>
+        <v>1.157536382999957</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02553523644396797</v>
+        <v>0.03698634286514927</v>
       </c>
       <c r="H38" t="n">
-        <v>1.293679535583239</v>
+        <v>0.2521433172925335</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.01865768933743828</v>
+        <v>0.001638915171032762</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.02212946343904232</v>
+        <v>-0.007422642542599611</v>
       </c>
       <c r="O38" t="n">
-        <v>-0</v>
+        <v>-0.001162724694842286</v>
       </c>
       <c r="P38" t="n">
-        <v>-0</v>
+        <v>-0.007978198098155167</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0</v>
+        <v>-0.009140922792997453</v>
       </c>
       <c r="R38" t="n">
-        <v>112.642010236361</v>
+        <v>108.7754263932512</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>54.52947235107422</v>
+        <v>177.6033935546875</v>
       </c>
       <c r="B39" t="n">
-        <v>1.355921030044556</v>
+        <v>298.1319274902344</v>
       </c>
       <c r="C39" t="n">
-        <v>3.998741332585895</v>
+        <v>5.179552938228487</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3044809503920702</v>
+        <v>5.697536098237152</v>
       </c>
       <c r="E39" t="n">
-        <v>3.732659325178731</v>
+        <v>1.141872357734086</v>
       </c>
       <c r="F39" t="n">
-        <v>3.693082561069468</v>
+        <v>1.162921527819081</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02694820021951632</v>
+        <v>0.02343835166683853</v>
       </c>
       <c r="H39" t="n">
-        <v>1.468623647845734</v>
+        <v>-0.8980652899229359</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.01960115404510421</v>
+        <v>-0.03010783008903128</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.03287898056785921</v>
+        <v>-0.007843663772585718</v>
       </c>
       <c r="O39" t="n">
-        <v>-0</v>
+        <v>0.03018719516839636</v>
       </c>
       <c r="P39" t="n">
-        <v>-0</v>
+        <v>-0.007843663772585718</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0</v>
+        <v>0.02234353139581064</v>
       </c>
       <c r="R39" t="n">
-        <v>112.642010236361</v>
+        <v>111.2058535479615</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>54.54058456420898</v>
+        <v>182.427490234375</v>
       </c>
       <c r="B40" t="n">
-        <v>1.39097797870636</v>
+        <v>306.1770935058594</v>
       </c>
       <c r="C40" t="n">
-        <v>3.99894509544231</v>
+        <v>5.206352780288265</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3300070815480963</v>
+        <v>5.724163671495992</v>
       </c>
       <c r="E40" t="n">
-        <v>3.710556128566621</v>
+        <v>1.149802001589033</v>
       </c>
       <c r="F40" t="n">
-        <v>3.693634207872385</v>
+        <v>1.164005470003465</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02719874411786726</v>
+        <v>0.0222136362277263</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6221581636601987</v>
+        <v>-0.6394031246763658</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0002037836174761942</v>
+        <v>0.02716218751868649</v>
       </c>
       <c r="N40" t="n">
-        <v>0.02585471268975903</v>
+        <v>0.02698525476070834</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.02668599704249601</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0.02642969920515279</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>0.0002562978373432251</v>
       </c>
       <c r="R40" t="n">
-        <v>112.642010236361</v>
+        <v>111.2343553677258</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>54.77610778808594</v>
+        <v>184.5449066162109</v>
       </c>
       <c r="B41" t="n">
-        <v>1.360563039779663</v>
+        <v>306.8567199707031</v>
       </c>
       <c r="C41" t="n">
-        <v>4.00325410961451</v>
+        <v>5.217892830158336</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3078986139116606</v>
+        <v>5.726380928450948</v>
       </c>
       <c r="E41" t="n">
-        <v>3.734185449778798</v>
+        <v>1.159770744986512</v>
       </c>
       <c r="F41" t="n">
-        <v>3.696727196060897</v>
+        <v>1.164514479648331</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02814874078481269</v>
+        <v>0.02198136564386955</v>
       </c>
       <c r="H41" t="n">
-        <v>1.330725733142262</v>
+        <v>-0.2158070949127911</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.00431831132282201</v>
+        <v>0.0116068931229365</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.02186586660055057</v>
+        <v>0.002219716886922241</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.01152752804357142</v>
       </c>
       <c r="P41" t="n">
-        <v>-0</v>
+        <v>-0.002219716886922241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>0.009307811156649181</v>
       </c>
       <c r="R41" t="n">
-        <v>112.642010236361</v>
+        <v>112.2697037416201</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>56.7926139831543</v>
+        <v>185.8134307861328</v>
       </c>
       <c r="B42" t="n">
-        <v>1.430220007896423</v>
+        <v>308.5157470703125</v>
       </c>
       <c r="C42" t="n">
-        <v>4.039406281763909</v>
+        <v>5.224743110021964</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3578282841136811</v>
+        <v>5.731772886030789</v>
       </c>
       <c r="E42" t="n">
-        <v>3.726704721875094</v>
+        <v>1.162799899009847</v>
       </c>
       <c r="F42" t="n">
-        <v>3.698786245781496</v>
+        <v>1.164938422109571</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02878506664914809</v>
+        <v>0.02185582844821663</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9698944398457316</v>
+        <v>-0.09784681028178788</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03681360864247019</v>
+        <v>0.006873796699033097</v>
       </c>
       <c r="N42" t="n">
-        <v>0.05119716329207424</v>
+        <v>0.005406520345286214</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>0.006794431619668018</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>-0.005406520345286214</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>0.001387911274381803</v>
       </c>
       <c r="R42" t="n">
-        <v>112.642010236361</v>
+        <v>112.4255241292147</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>55.47148895263672</v>
+        <v>182.9268035888672</v>
       </c>
       <c r="B43" t="n">
-        <v>1.403051972389221</v>
+        <v>303.3687744140625</v>
       </c>
       <c r="C43" t="n">
-        <v>4.015869176191778</v>
+        <v>5.209086092439224</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3386498441899025</v>
+        <v>5.714949142745352</v>
       </c>
       <c r="E43" t="n">
-        <v>3.719927409607883</v>
+        <v>1.159065386240345</v>
       </c>
       <c r="F43" t="n">
-        <v>3.699101227053893</v>
+        <v>1.163918962497083</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02898975722958715</v>
+        <v>0.02161731190045196</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7183979634273848</v>
+        <v>-0.2245226547633881</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.02326226841591494</v>
+        <v>-0.01553508368610912</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.01899570370796388</v>
+        <v>-0.01668301441701447</v>
       </c>
       <c r="O43" t="n">
-        <v>-0</v>
+        <v>-0.0156144487654742</v>
       </c>
       <c r="P43" t="n">
-        <v>-0</v>
+        <v>0.01668301441701447</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0</v>
+        <v>0.001068565651540275</v>
       </c>
       <c r="R43" t="n">
-        <v>112.642010236361</v>
+        <v>112.5456581826555</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>53.81081008911133</v>
+        <v>180.0401611328125</v>
       </c>
       <c r="B44" t="n">
-        <v>1.363571047782898</v>
+        <v>302.0995483398438</v>
       </c>
       <c r="C44" t="n">
-        <v>3.985474378008178</v>
+        <v>5.193179943407737</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3101070288641382</v>
+        <v>5.710756593323133</v>
       </c>
       <c r="E44" t="n">
-        <v>3.714475812597138</v>
+        <v>1.146130376854661</v>
       </c>
       <c r="F44" t="n">
-        <v>3.69699672087535</v>
+        <v>1.162853680447254</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0259689294333032</v>
+        <v>0.02195716270390204</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6730771003356081</v>
+        <v>-0.7616331772056054</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.02993752096583036</v>
+        <v>-0.01578031430835303</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.02813931727638874</v>
+        <v>-0.004183772956429577</v>
       </c>
       <c r="O44" t="n">
-        <v>-0</v>
+        <v>-0.01585967938771811</v>
       </c>
       <c r="P44" t="n">
-        <v>-0</v>
+        <v>0.004183772956429577</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0</v>
+        <v>-0.01167590643128853</v>
       </c>
       <c r="R44" t="n">
-        <v>112.642010236361</v>
+        <v>111.2315856084671</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>53.72039413452148</v>
+        <v>183.0067138671875</v>
       </c>
       <c r="B45" t="n">
-        <v>1.361842036247253</v>
+        <v>305.3775939941406</v>
       </c>
       <c r="C45" t="n">
-        <v>3.983792708458381</v>
+        <v>5.209522839967279</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3088382217407461</v>
+        <v>5.721549023996647</v>
       </c>
       <c r="E45" t="n">
-        <v>3.713902937360975</v>
+        <v>1.15482498703296</v>
       </c>
       <c r="F45" t="n">
-        <v>3.699148874270183</v>
+        <v>1.162962017903124</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02546759601801986</v>
+        <v>0.02190950408473793</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5793268858337743</v>
+        <v>-0.3713927452986963</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.001680256335857333</v>
+        <v>0.01647717218041489</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.001268002527961998</v>
+        <v>0.01085087903080639</v>
       </c>
       <c r="O45" t="n">
-        <v>-0</v>
+        <v>0.01639780710104981</v>
       </c>
       <c r="P45" t="n">
-        <v>-0</v>
+        <v>-0.01085087903080639</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0</v>
+        <v>0.005546928070243418</v>
       </c>
       <c r="R45" t="n">
-        <v>112.642010236361</v>
+        <v>111.8485792129763</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>53.84933090209961</v>
+        <v>181.7182006835938</v>
       </c>
       <c r="B46" t="n">
-        <v>1.386425018310547</v>
+        <v>310.7344055175781</v>
       </c>
       <c r="C46" t="n">
-        <v>3.986189978308855</v>
+        <v>5.20245713925509</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3267285047776085</v>
+        <v>5.738938545760967</v>
       </c>
       <c r="E46" t="n">
-        <v>3.70066611773097</v>
+        <v>1.135435830510881</v>
       </c>
       <c r="F46" t="n">
-        <v>3.700181301886968</v>
+        <v>1.161082123031368</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02506659278651863</v>
+        <v>0.02260190090996305</v>
       </c>
       <c r="H46" t="n">
-        <v>0.01934111461141958</v>
+        <v>-1.134696263940445</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M46" t="n">
-        <v>0.002400145599364967</v>
+        <v>-0.007040797336696936</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01805127276804819</v>
+        <v>0.01754159974009184</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-0.007120162416062015</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>-0.01754159974009184</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>-0.02466176215615385</v>
       </c>
       <c r="R46" t="n">
-        <v>112.642010236361</v>
+        <v>109.0901961549222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>54.74279403686523</v>
+        <v>180.1899871826172</v>
       </c>
       <c r="B47" t="n">
-        <v>1.38487696647644</v>
+        <v>307.5063171386719</v>
       </c>
       <c r="C47" t="n">
-        <v>4.002645744269477</v>
+        <v>5.194011778606122</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3256113028244327</v>
+        <v>5.728495630575953</v>
       </c>
       <c r="E47" t="n">
-        <v>3.718098192186417</v>
+        <v>1.134391064631173</v>
       </c>
       <c r="F47" t="n">
-        <v>3.701950911346453</v>
+        <v>1.158496259909553</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0250172003340178</v>
+        <v>0.02254637386938444</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6454471573306951</v>
+        <v>-1.069138452951516</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0165919078250012</v>
+        <v>-0.008409798772097021</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.001116578115412881</v>
+        <v>-0.0103885772595067</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>-0.008489163851462101</v>
       </c>
       <c r="P47" t="n">
-        <v>-0</v>
+        <v>0.0103885772595067</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.001899413408044602</v>
       </c>
       <c r="R47" t="n">
-        <v>112.642010236361</v>
+        <v>109.2974035361851</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>54.57498931884766</v>
+        <v>178.3521270751953</v>
       </c>
       <c r="B48" t="n">
-        <v>1.384649038314819</v>
+        <v>306.9466552734375</v>
       </c>
       <c r="C48" t="n">
-        <v>3.999575706720874</v>
+        <v>5.183759838143623</v>
       </c>
       <c r="D48" t="n">
-        <v>0.325446705588847</v>
+        <v>5.726673971164641</v>
       </c>
       <c r="E48" t="n">
-        <v>3.715171994056347</v>
+        <v>1.1254300819972</v>
       </c>
       <c r="F48" t="n">
-        <v>3.703612185009954</v>
+        <v>1.155427514002425</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02472029926698208</v>
+        <v>0.02266702199691337</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4676241546085416</v>
+        <v>-1.323395371889162</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.003065329802212413</v>
+        <v>-0.01019956844527248</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.00016458369020389</v>
+        <v>-0.001820001196859988</v>
       </c>
       <c r="O48" t="n">
-        <v>-0</v>
+        <v>-0.01027893352463756</v>
       </c>
       <c r="P48" t="n">
-        <v>-0</v>
+        <v>0.001820001196859988</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0</v>
+        <v>-0.00845893232777757</v>
       </c>
       <c r="R48" t="n">
-        <v>112.642010236361</v>
+        <v>108.3728641960707</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>55.30593490600586</v>
+        <v>172.4989471435547</v>
       </c>
       <c r="B49" t="n">
-        <v>1.398908019065857</v>
+        <v>300.8203125</v>
       </c>
       <c r="C49" t="n">
-        <v>4.012880224758953</v>
+        <v>5.150391132937163</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3356919458920362</v>
+        <v>5.706513118053733</v>
       </c>
       <c r="E49" t="n">
-        <v>3.71952332765799</v>
+        <v>1.106348795718598</v>
       </c>
       <c r="F49" t="n">
-        <v>3.704483020788528</v>
+        <v>1.152287910976077</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02496998338279852</v>
+        <v>0.02490572384815192</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6023354777169491</v>
+        <v>-1.844520381642619</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01339341695309804</v>
+        <v>-0.03281811115811839</v>
       </c>
       <c r="N49" t="n">
-        <v>0.01029790246948892</v>
+        <v>-0.01995898201913937</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>-0.03289747623748347</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.01995898201913937</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>-0.0129384942183441</v>
       </c>
       <c r="R49" t="n">
-        <v>112.642010236361</v>
+        <v>106.9706825192444</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58.72369003295898</v>
+        <v>175.4355316162109</v>
       </c>
       <c r="B50" t="n">
-        <v>1.543565034866333</v>
+        <v>301.8796997070312</v>
       </c>
       <c r="C50" t="n">
-        <v>4.072843223492582</v>
+        <v>5.167271634201437</v>
       </c>
       <c r="D50" t="n">
-        <v>0.434094698744502</v>
+        <v>5.710028592673332</v>
       </c>
       <c r="E50" t="n">
-        <v>3.693493419513012</v>
+        <v>1.120737980849365</v>
       </c>
       <c r="F50" t="n">
-        <v>3.703652137124695</v>
+        <v>1.149019342238418</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02504920433771122</v>
+        <v>0.02452007090885564</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4055505106958159</v>
+        <v>-1.153396394903525</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06179725797532765</v>
+        <v>0.0170237820072745</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1034070959841042</v>
+        <v>0.003521661147902977</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.01694441692790942</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>-0.003521661147902977</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.01342275578000645</v>
       </c>
       <c r="R50" t="n">
-        <v>112.642010236361</v>
+        <v>108.4065238663208</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>58.09467315673828</v>
+        <v>174.9960327148438</v>
       </c>
       <c r="B51" t="n">
-        <v>1.51854395866394</v>
+        <v>290.2666320800781</v>
       </c>
       <c r="C51" t="n">
-        <v>4.062073975605371</v>
+        <v>5.164763303465648</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4177519538261417</v>
+        <v>5.670799921537744</v>
       </c>
       <c r="E51" t="n">
-        <v>3.697005887341747</v>
+        <v>1.146029885322577</v>
       </c>
       <c r="F51" t="n">
-        <v>3.706112889399291</v>
+        <v>1.146609998434266</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02142842727282507</v>
+        <v>0.02209247915858113</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4249962884160591</v>
+        <v>-0.0262583980514092</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.01071146714158566</v>
+        <v>-0.00250518750288653</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01620992678456168</v>
+        <v>-0.03846919033715546</v>
       </c>
       <c r="O51" t="n">
-        <v>-0</v>
+        <v>-0.002584552582251609</v>
       </c>
       <c r="P51" t="n">
-        <v>-0</v>
+        <v>0.03846919033715546</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0</v>
+        <v>0.03588463775490384</v>
       </c>
       <c r="R51" t="n">
-        <v>112.642010236361</v>
+        <v>112.2966527055321</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>56.05348205566406</v>
+        <v>178.4719848632812</v>
       </c>
       <c r="B52" t="n">
-        <v>1.46385395526886</v>
+        <v>290.7563171386719</v>
       </c>
       <c r="C52" t="n">
-        <v>4.026306271686033</v>
+        <v>5.184431641357496</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3810726532330127</v>
+        <v>5.672485518208908</v>
       </c>
       <c r="E52" t="n">
-        <v>3.69329175498261</v>
+        <v>1.164503689151217</v>
       </c>
       <c r="F52" t="n">
-        <v>3.707361014862619</v>
+        <v>1.144653830976878</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01977504251995214</v>
+        <v>0.0181603741298513</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.7114654679409117</v>
+        <v>1.093031345742516</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.03513559832873359</v>
+        <v>0.01986303400432843</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.03601476472449205</v>
+        <v>0.001687018087765058</v>
       </c>
       <c r="O52" t="n">
-        <v>-0</v>
+        <v>0.01978366892496335</v>
       </c>
       <c r="P52" t="n">
-        <v>-0</v>
+        <v>-0.001687018087765058</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0</v>
+        <v>0.01809665083719829</v>
       </c>
       <c r="R52" t="n">
-        <v>112.642010236361</v>
+        <v>114.3288460197302</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>55.50734710693359</v>
+        <v>171.0406646728516</v>
       </c>
       <c r="B53" t="n">
-        <v>1.447322964668274</v>
+        <v>280.7523193359375</v>
       </c>
       <c r="C53" t="n">
-        <v>4.016515392295999</v>
+        <v>5.141901333335903</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3697156187837066</v>
+        <v>5.63747285479881</v>
       </c>
       <c r="E53" t="n">
-        <v>3.693425642710429</v>
+        <v>1.146785852465449</v>
       </c>
       <c r="F53" t="n">
-        <v>3.708738589129907</v>
+        <v>1.143986406210321</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01756952334581055</v>
+        <v>0.01780327376817853</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.8715629967917733</v>
+        <v>0.1572433413977867</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.009743104776044564</v>
+        <v>-0.04163858095780393</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.01129278678455992</v>
+        <v>-0.03440681152238945</v>
       </c>
       <c r="O53" t="n">
-        <v>-0</v>
+        <v>0.04211477143399441</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>-0.034962367077945</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0</v>
+        <v>0.007152404356049406</v>
       </c>
       <c r="R53" t="n">
-        <v>112.642010236361</v>
+        <v>115.1465721560238</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56.17632293701172</v>
+        <v>167.3249816894531</v>
       </c>
       <c r="B54" t="n">
-        <v>1.44546103477478</v>
+        <v>274.1762390136719</v>
       </c>
       <c r="C54" t="n">
-        <v>4.028495368074672</v>
+        <v>5.119937919555671</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3684283258845668</v>
+        <v>5.613771107697508</v>
       </c>
       <c r="E54" t="n">
-        <v>3.706530567285678</v>
+        <v>1.141619187726321</v>
       </c>
       <c r="F54" t="n">
-        <v>3.709117922667565</v>
+        <v>1.14568891359565</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01742825343804178</v>
+        <v>0.01563326937483945</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.148457525654241</v>
+        <v>-0.2603246814053702</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.01205202310946984</v>
+        <v>-0.0217239741818438</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.001286464693055156</v>
+        <v>-0.02342306677223538</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>0.02180333926120888</v>
       </c>
       <c r="P54" t="n">
-        <v>-0</v>
+        <v>-0.02342306677223538</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.001619727511026504</v>
       </c>
       <c r="R54" t="n">
-        <v>112.642010236361</v>
+        <v>114.9600660853023</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55.66477584838867</v>
+        <v>164.9777221679688</v>
       </c>
       <c r="B55" t="n">
-        <v>1.431877970695496</v>
+        <v>273.3367309570312</v>
       </c>
       <c r="C55" t="n">
-        <v>4.019347556376347</v>
+        <v>5.105810447621117</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3589868489125991</v>
+        <v>5.610704481843535</v>
       </c>
       <c r="E55" t="n">
-        <v>3.705633541530957</v>
+        <v>1.129664945666003</v>
       </c>
       <c r="F55" t="n">
-        <v>3.710724500581521</v>
+        <v>1.144722185336248</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01532655119595127</v>
+        <v>0.0160110148582519</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3321659899527291</v>
+        <v>-0.9404300604021204</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.009106097762871079</v>
+        <v>-0.01402814748750891</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.009397046169010714</v>
+        <v>-0.003061928559749294</v>
       </c>
       <c r="O55" t="n">
-        <v>-0</v>
+        <v>-0.01450433796369939</v>
       </c>
       <c r="P55" t="n">
-        <v>-0</v>
+        <v>0.003617484115304849</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0</v>
+        <v>-0.01088685384839454</v>
       </c>
       <c r="R55" t="n">
-        <v>112.642010236361</v>
+        <v>113.7085126474298</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56.38277435302734</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="B56" t="n">
-        <v>1.415423989295959</v>
+        <v>287.3883361816406</v>
       </c>
       <c r="C56" t="n">
-        <v>4.032163692581483</v>
+        <v>5.160186703234448</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3474291252907944</v>
+        <v>5.66083438890224</v>
       </c>
       <c r="E56" t="n">
-        <v>3.728549824554431</v>
+        <v>1.148515572526311</v>
       </c>
       <c r="F56" t="n">
-        <v>3.713477972141172</v>
+        <v>1.145026785859405</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01306289804067701</v>
+        <v>0.01602292736720544</v>
       </c>
       <c r="H56" t="n">
-        <v>1.153790863736834</v>
+        <v>0.2177371579456638</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.01289861485464794</v>
+        <v>0.05588180888236938</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01149118970769836</v>
+        <v>0.05140767278298308</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>0.0558024438030043</v>
       </c>
       <c r="P56" t="n">
-        <v>-0</v>
+        <v>-0.05140767278298308</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.004394771020021213</v>
       </c>
       <c r="R56" t="n">
-        <v>112.642010236361</v>
+        <v>114.2082355235425</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56.62164306640625</v>
+        <v>175.54541015625</v>
       </c>
       <c r="B57" t="n">
-        <v>1.414237976074219</v>
+        <v>297.2124938964844</v>
       </c>
       <c r="C57" t="n">
-        <v>4.036391298450382</v>
+        <v>5.167897756765663</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3465908532245856</v>
+        <v>5.694447350642657</v>
       </c>
       <c r="E57" t="n">
-        <v>3.733509985658206</v>
+        <v>1.132406083189149</v>
       </c>
       <c r="F57" t="n">
-        <v>3.714027584276882</v>
+        <v>1.143649848269309</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01367993043723843</v>
+        <v>0.01585587161762223</v>
       </c>
       <c r="H57" t="n">
-        <v>1.424159389604143</v>
+        <v>-0.7091231154812994</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.004236554800997938</v>
+        <v>0.007740860269023653</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.0008379208143354244</v>
+        <v>0.03418426038221156</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>-0.007264669792833176</v>
       </c>
       <c r="P57" t="n">
-        <v>-0</v>
+        <v>0.03362870482665601</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.02636403503382283</v>
       </c>
       <c r="R57" t="n">
-        <v>112.642010236361</v>
+        <v>117.2192254460362</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>54.56801223754883</v>
+        <v>177.1834869384766</v>
       </c>
       <c r="B58" t="n">
-        <v>1.360113978385925</v>
+        <v>295.5934448242188</v>
       </c>
       <c r="C58" t="n">
-        <v>3.99944785461476</v>
+        <v>5.177185844993849</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3075685038730066</v>
+        <v>5.688985012996693</v>
       </c>
       <c r="E58" t="n">
-        <v>3.730667673718822</v>
+        <v>1.145565173593878</v>
       </c>
       <c r="F58" t="n">
-        <v>3.714398985694642</v>
+        <v>1.142584994839778</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0140393079104686</v>
+        <v>0.01490132387907618</v>
       </c>
       <c r="H58" t="n">
-        <v>1.158795585076427</v>
+        <v>0.1999942272434325</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.03626936128379232</v>
+        <v>0.009331356375359201</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.03827078511817095</v>
+        <v>-0.005447446206045203</v>
       </c>
       <c r="O58" t="n">
-        <v>-0</v>
+        <v>0.008855165899168724</v>
       </c>
       <c r="P58" t="n">
-        <v>-0</v>
+        <v>0.006003001761600759</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0</v>
+        <v>0.01485816766076948</v>
       </c>
       <c r="R58" t="n">
-        <v>112.642010236361</v>
+        <v>118.960888350779</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>53.68352127075195</v>
+        <v>177.4331970214844</v>
       </c>
       <c r="B59" t="n">
-        <v>1.325013995170593</v>
+        <v>299.8109130859375</v>
       </c>
       <c r="C59" t="n">
-        <v>3.983106087955226</v>
+        <v>5.178594183267687</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2814230217753044</v>
+        <v>5.703151986226595</v>
       </c>
       <c r="E59" t="n">
-        <v>3.73717410939256</v>
+        <v>1.136933783868018</v>
       </c>
       <c r="F59" t="n">
-        <v>3.714624724905334</v>
+        <v>1.142338066146475</v>
       </c>
       <c r="G59" t="n">
-        <v>0.01438052093165645</v>
+        <v>0.01495457766889422</v>
       </c>
       <c r="H59" t="n">
-        <v>1.568050600836531</v>
+        <v>-0.3613797994240637</v>
       </c>
       <c r="I59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.01620896438276798</v>
+        <v>0.001409330447901924</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.02580664839353086</v>
+        <v>0.0142678003709682</v>
       </c>
       <c r="O59" t="n">
-        <v>-0</v>
+        <v>-0.0009331399717114481</v>
       </c>
       <c r="P59" t="n">
-        <v>-0</v>
+        <v>0.01371224481541264</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0</v>
+        <v>0.01277910484370119</v>
       </c>
       <c r="R59" t="n">
-        <v>112.642010236361</v>
+        <v>120.4811020153134</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>53.19775390625</v>
+        <v>177.8926696777344</v>
       </c>
       <c r="B60" t="n">
-        <v>1.322582960128784</v>
+        <v>305.2776489257812</v>
       </c>
       <c r="C60" t="n">
-        <v>3.974016175648987</v>
+        <v>5.181180389088362</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2795866125589055</v>
+        <v>5.721221686860314</v>
       </c>
       <c r="E60" t="n">
-        <v>3.729689011607856</v>
+        <v>1.126714510603324</v>
       </c>
       <c r="F60" t="n">
-        <v>3.715581369057396</v>
+        <v>1.141183691597189</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01472781857585974</v>
+        <v>0.01523652470280289</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9578908429510847</v>
+        <v>-0.9496378784595011</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.009048723947372883</v>
+        <v>0.00258955293576979</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.001834724048704217</v>
+        <v>0.01823394546774471</v>
       </c>
       <c r="O60" t="n">
-        <v>0.009326501725150661</v>
+        <v>0.002113362459579314</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.002112501826481995</v>
+        <v>-0.01767838991218915</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.007213999898668666</v>
+        <v>-0.01556502745260984</v>
       </c>
       <c r="R60" t="n">
-        <v>113.4546096867919</v>
+        <v>118.6058103549244</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>53.91790771484375</v>
+        <v>181.8680419921875</v>
       </c>
       <c r="B61" t="n">
-        <v>1.340258955955505</v>
+        <v>317.1305847167969</v>
       </c>
       <c r="C61" t="n">
-        <v>3.987462662343085</v>
+        <v>5.203281380106307</v>
       </c>
       <c r="D61" t="n">
-        <v>0.29286284600537</v>
+        <v>5.759313628223341</v>
       </c>
       <c r="E61" t="n">
-        <v>3.731533567732267</v>
+        <v>1.121820834231199</v>
       </c>
       <c r="F61" t="n">
-        <v>3.71544877495507</v>
+        <v>1.139286196059424</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01456252103539482</v>
+        <v>0.01516282490123504</v>
       </c>
       <c r="H61" t="n">
-        <v>1.104533530842817</v>
+        <v>-1.151854086688159</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M61" t="n">
-        <v>0.01353729726752895</v>
+        <v>0.0223470271240227</v>
       </c>
       <c r="N61" t="n">
-        <v>0.01336475393951853</v>
+        <v>0.03882673963431005</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.0001984126984126984</v>
+        <v>0.02226766204465762</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0002777777777777778</v>
+        <v>-0.03882673963431005</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.936507936507937e-05</v>
+        <v>-0.01655907758965243</v>
       </c>
       <c r="R61" t="n">
-        <v>113.4636140208941</v>
+        <v>116.6418075386736</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>53.80585479736328</v>
+        <v>183.6959075927734</v>
       </c>
       <c r="B62" t="n">
-        <v>1.347766041755676</v>
+        <v>318.2998657226562</v>
       </c>
       <c r="C62" t="n">
-        <v>3.985382286476504</v>
+        <v>5.213281714307025</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2984484378984874</v>
+        <v>5.762993912430139</v>
       </c>
       <c r="E62" t="n">
-        <v>3.72457201456522</v>
+        <v>1.129213056466276</v>
       </c>
       <c r="F62" t="n">
-        <v>3.715342139589576</v>
+        <v>1.137606853932245</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01448335359739142</v>
+        <v>0.01425424043268824</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6372747108312774</v>
+        <v>-0.5888631881583976</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.002078213384560157</v>
+        <v>0.0100505046437156</v>
       </c>
       <c r="N62" t="n">
-        <v>0.005601220396112883</v>
+        <v>0.003687064768298942</v>
       </c>
       <c r="O62" t="n">
-        <v>-0</v>
+        <v>0.009971139564350516</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>-0.003687064768298942</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>0.006284074796051574</v>
       </c>
       <c r="R62" t="n">
-        <v>113.4636140208941</v>
+        <v>117.3747933815933</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>52.26017379760742</v>
+        <v>188.4104156494141</v>
       </c>
       <c r="B63" t="n">
-        <v>1.31869101524353</v>
+        <v>317.0506286621094</v>
       </c>
       <c r="C63" t="n">
-        <v>3.95623458572045</v>
+        <v>5.238622645377461</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2766395894645049</v>
+        <v>5.759061472992551</v>
       </c>
       <c r="E63" t="n">
-        <v>3.714482787461066</v>
+        <v>1.157340794689374</v>
       </c>
       <c r="F63" t="n">
-        <v>3.715069908482235</v>
+        <v>1.137520624354697</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01444374693794086</v>
+        <v>0.01412220188238889</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.04064880281350572</v>
+        <v>1.403475923920505</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.02872700388418703</v>
+        <v>0.02566474190101165</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.02157275492285826</v>
+        <v>-0.003924717522926557</v>
       </c>
       <c r="O63" t="n">
-        <v>-0</v>
+        <v>0.02558537682164657</v>
       </c>
       <c r="P63" t="n">
-        <v>-0</v>
+        <v>0.003924717522926557</v>
       </c>
       <c r="Q63" t="n">
-        <v>-0</v>
+        <v>0.02951009434457312</v>
       </c>
       <c r="R63" t="n">
-        <v>113.4636140208941</v>
+        <v>120.8385346079589</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>53.54297637939453</v>
+        <v>189.0896148681641</v>
       </c>
       <c r="B64" t="n">
-        <v>1.321220993995667</v>
+        <v>321.1181945800781</v>
       </c>
       <c r="C64" t="n">
-        <v>3.980484628242872</v>
+        <v>5.24222105542636</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2785563045048805</v>
+        <v>5.771809262772875</v>
       </c>
       <c r="E64" t="n">
-        <v>3.737057837229708</v>
+        <v>1.151905211385223</v>
       </c>
       <c r="F64" t="n">
-        <v>3.716199009713864</v>
+        <v>1.137809366081225</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01525473758230754</v>
+        <v>0.01436445943872254</v>
       </c>
       <c r="H64" t="n">
-        <v>1.367367180411997</v>
+        <v>0.9813000874923367</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0245464660480299</v>
+        <v>0.003604892099032586</v>
       </c>
       <c r="N64" t="n">
-        <v>0.001918553112814747</v>
+        <v>0.01282938922131471</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>-0.00312870162284211</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.01227383366575916</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>0.009145132042917047</v>
       </c>
       <c r="R64" t="n">
-        <v>113.4636140208941</v>
+        <v>121.9436189628213</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55.40741729736328</v>
+        <v>196.2812347412109</v>
       </c>
       <c r="B65" t="n">
-        <v>1.381489992141724</v>
+        <v>332.7112731933594</v>
       </c>
       <c r="C65" t="n">
-        <v>4.014713471025271</v>
+        <v>5.279548501915238</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3231626211580074</v>
+        <v>5.807275066409984</v>
       </c>
       <c r="E65" t="n">
-        <v>3.732305790525194</v>
+        <v>1.164099059043286</v>
       </c>
       <c r="F65" t="n">
-        <v>3.717119152372075</v>
+        <v>1.138273069681741</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01565862221710396</v>
+        <v>0.01507478267880549</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9698578803779268</v>
+        <v>1.713191487520092</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.03482139104030568</v>
+        <v>0.03803286541178363</v>
       </c>
       <c r="N65" t="n">
-        <v>0.04561613720940838</v>
+        <v>0.03610221659486279</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>-0.03795350033241855</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.03610221659486279</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>-0.001851283737555762</v>
       </c>
       <c r="R65" t="n">
-        <v>113.4636140208941</v>
+        <v>121.7178667241367</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>53.96843338012695</v>
+        <v>198.6384887695312</v>
       </c>
       <c r="B66" t="n">
-        <v>1.342373013496399</v>
+        <v>336.9187622070312</v>
       </c>
       <c r="C66" t="n">
-        <v>3.988399308603664</v>
+        <v>5.291486533285003</v>
       </c>
       <c r="D66" t="n">
-        <v>0.2944389533526298</v>
+        <v>5.819841839592116</v>
       </c>
       <c r="E66" t="n">
-        <v>3.73109287394478</v>
+        <v>1.167131378336443</v>
       </c>
       <c r="F66" t="n">
-        <v>3.718640490182765</v>
+        <v>1.139857847073019</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0154526947335325</v>
+        <v>0.01637111391919556</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8058389799801964</v>
+        <v>1.665954521973309</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.02597096178501734</v>
+        <v>0.01200957407583192</v>
       </c>
       <c r="N66" t="n">
-        <v>-0.02831506479803136</v>
+        <v>0.01264606688342251</v>
       </c>
       <c r="O66" t="n">
-        <v>-0</v>
+        <v>-0.01193020899646684</v>
       </c>
       <c r="P66" t="n">
-        <v>-0</v>
+        <v>0.01264606688342251</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0.0007158578869556741</v>
       </c>
       <c r="R66" t="n">
-        <v>113.4636140208941</v>
+        <v>121.8049994190146</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>54.50248336791992</v>
+        <v>198.1190948486328</v>
       </c>
       <c r="B67" t="n">
-        <v>1.344143986701965</v>
+        <v>335.8193969726562</v>
       </c>
       <c r="C67" t="n">
-        <v>3.998246267014934</v>
+        <v>5.288868339006959</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2957573693254036</v>
+        <v>5.816573506443499</v>
       </c>
       <c r="E67" t="n">
-        <v>3.739787685503574</v>
+        <v>1.166829358112802</v>
       </c>
       <c r="F67" t="n">
-        <v>3.719724964848623</v>
+        <v>1.141479761747101</v>
       </c>
       <c r="G67" t="n">
-        <v>0.01615764084008913</v>
+        <v>0.01737696388212505</v>
       </c>
       <c r="H67" t="n">
-        <v>1.241686261844176</v>
+        <v>1.458804687496509</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.009895599229856833</v>
+        <v>-0.002614769796708716</v>
       </c>
       <c r="N67" t="n">
-        <v>0.001319285465188003</v>
+        <v>-0.003262997961803848</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>0.002694134876073795</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-0.003262997961803848</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>-0.0005688630857300534</v>
       </c>
       <c r="R67" t="n">
-        <v>113.4636140208941</v>
+        <v>121.7357090511878</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>54.96680068969727</v>
+        <v>201.4452056884766</v>
       </c>
       <c r="B68" t="n">
-        <v>1.356606006622314</v>
+        <v>341.4760437011719</v>
       </c>
       <c r="C68" t="n">
-        <v>4.006729379154579</v>
+        <v>5.305517412339395</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3049859972233529</v>
+        <v>5.833277526334015</v>
       </c>
       <c r="E68" t="n">
-        <v>3.740206017782481</v>
+        <v>1.171640771171528</v>
       </c>
       <c r="F68" t="n">
-        <v>3.72097666603493</v>
+        <v>1.143790296205817</v>
       </c>
       <c r="G68" t="n">
-        <v>0.01674534760506904</v>
+        <v>0.01818406109637965</v>
       </c>
       <c r="H68" t="n">
-        <v>1.148339956928139</v>
+        <v>1.531587186057967</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0.008519195696881532</v>
+        <v>0.01678844153000481</v>
       </c>
       <c r="N68" t="n">
-        <v>0.009271342983816933</v>
+        <v>0.01684431209009718</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>-0.01670907645063973</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>0.01684431209009718</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>0.0001352356394574532</v>
       </c>
       <c r="R68" t="n">
-        <v>113.4636140208941</v>
+        <v>121.7521720576461</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>54.65038681030273</v>
+        <v>201.8247680664062</v>
       </c>
       <c r="B69" t="n">
-        <v>1.376665949821472</v>
+        <v>337.2185974121094</v>
       </c>
       <c r="C69" t="n">
-        <v>4.000956292553633</v>
+        <v>5.307399836098733</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3196645975939011</v>
+        <v>5.820731377074562</v>
       </c>
       <c r="E69" t="n">
-        <v>3.721605490096983</v>
+        <v>1.18241429142441</v>
       </c>
       <c r="F69" t="n">
-        <v>3.721080774156879</v>
+        <v>1.147593570991108</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01674230871195119</v>
+        <v>0.01789323681001069</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0313407158553647</v>
+        <v>1.946026915254459</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.005756454358345819</v>
+        <v>0.00188419663120043</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0147868600767167</v>
+        <v>-0.01246777443863156</v>
       </c>
       <c r="O69" t="n">
-        <v>-0</v>
+        <v>-0.001804831551835351</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>-0.01246777443863156</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>-0.01427260599046691</v>
       </c>
       <c r="R69" t="n">
-        <v>113.4636140208941</v>
+        <v>120.0144512773838</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>54.31154251098633</v>
+        <v>199.6473236083984</v>
       </c>
       <c r="B70" t="n">
-        <v>1.361827969551086</v>
+        <v>332.0916442871094</v>
       </c>
       <c r="C70" t="n">
-        <v>3.994736773613345</v>
+        <v>5.296552428001888</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3088278925186765</v>
+        <v>5.805410967834648</v>
       </c>
       <c r="E70" t="n">
-        <v>3.724856029090966</v>
+        <v>1.18242401837799</v>
       </c>
       <c r="F70" t="n">
-        <v>3.722648904635777</v>
+        <v>1.150677872867539</v>
       </c>
       <c r="G70" t="n">
-        <v>0.015440553011492</v>
+        <v>0.018331551071787</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1429433553025499</v>
+        <v>1.731776290294916</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.006200217767763805</v>
+        <v>-0.01078878711898912</v>
       </c>
       <c r="N70" t="n">
-        <v>-0.01077819951333148</v>
+        <v>-0.01520364880331448</v>
       </c>
       <c r="O70" t="n">
-        <v>-0</v>
+        <v>0.0108681521983542</v>
       </c>
       <c r="P70" t="n">
-        <v>-0</v>
+        <v>-0.01520364880331448</v>
       </c>
       <c r="Q70" t="n">
-        <v>-0</v>
+        <v>-0.004335496604960286</v>
       </c>
       <c r="R70" t="n">
-        <v>113.4636140208941</v>
+        <v>119.4941290313245</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>55.13288497924805</v>
+        <v>202.2642669677734</v>
       </c>
       <c r="B71" t="n">
-        <v>1.391667008399963</v>
+        <v>339.1174621582031</v>
       </c>
       <c r="C71" t="n">
-        <v>4.009746361710326</v>
+        <v>5.309575094700491</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3305023151915389</v>
+        <v>5.826346543406457</v>
       </c>
       <c r="E71" t="n">
-        <v>3.72092461648902</v>
+        <v>1.180610242538928</v>
       </c>
       <c r="F71" t="n">
-        <v>3.723844841093141</v>
+        <v>1.152406890728356</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01422859689458506</v>
+        <v>0.01946578974822397</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.205236301636492</v>
+        <v>1.448867586435582</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01512279766489</v>
+        <v>0.01310783090940926</v>
       </c>
       <c r="N71" t="n">
-        <v>0.02191101924475314</v>
+        <v>0.02115626211004451</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>-0.01302846583004418</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.02115626211004451</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>0.008127796280000333</v>
       </c>
       <c r="R71" t="n">
-        <v>113.4636140208941</v>
+        <v>120.4653529687472</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56.36906814575195</v>
+        <v>199.4075927734375</v>
       </c>
       <c r="B72" t="n">
-        <v>1.452635049819946</v>
+        <v>338.6877136230469</v>
       </c>
       <c r="C72" t="n">
-        <v>4.031920570925302</v>
+        <v>5.295350934904278</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3733791829226129</v>
+        <v>5.825078484064047</v>
       </c>
       <c r="E72" t="n">
-        <v>3.705629279505703</v>
+        <v>1.167284720064792</v>
       </c>
       <c r="F72" t="n">
-        <v>3.724461717319295</v>
+        <v>1.152545942274035</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0130531530969657</v>
+        <v>0.01956642264448924</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.442750090625193</v>
+        <v>0.7532689065626484</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.02242188427050751</v>
+        <v>-0.01412347438903327</v>
       </c>
       <c r="N72" t="n">
-        <v>0.04380936032253824</v>
+        <v>-0.001267255694888836</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>0.01420283946839835</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>-0.001267255694888836</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>0.01293558377350952</v>
       </c>
       <c r="R72" t="n">
-        <v>113.4636140208941</v>
+        <v>122.0236426338798</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56.47679138183594</v>
+        <v>208.0275421142578</v>
       </c>
       <c r="B73" t="n">
-        <v>1.477049946784973</v>
+        <v>344.1943969726562</v>
       </c>
       <c r="C73" t="n">
-        <v>4.033829781759562</v>
+        <v>5.337670484946211</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3900468193518715</v>
+        <v>5.841206605238948</v>
       </c>
       <c r="E73" t="n">
-        <v>3.69297285608889</v>
+        <v>1.198174732751464</v>
       </c>
       <c r="F73" t="n">
-        <v>3.724439077988218</v>
+        <v>1.155115386288336</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01311008353050202</v>
+        <v>0.02199380300511742</v>
       </c>
       <c r="H73" t="n">
-        <v>-2.400154188653204</v>
+        <v>1.957794495709034</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.001911034537690925</v>
+        <v>0.04322778897699298</v>
       </c>
       <c r="N73" t="n">
-        <v>0.01680731644748157</v>
+        <v>0.01625888134737075</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>-0.04314842389762789</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.01625888134737075</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>-0.02688954255025715</v>
       </c>
       <c r="R73" t="n">
-        <v>113.4636140208941</v>
+        <v>118.7424827031387</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>55.03650283813477</v>
+        <v>216.3578338623047</v>
       </c>
       <c r="B74" t="n">
-        <v>1.42487096786499</v>
+        <v>350.130859375</v>
       </c>
       <c r="C74" t="n">
-        <v>4.007996653055098</v>
+        <v>5.376933675224068</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3540812607541442</v>
+        <v>5.858306968534851</v>
       </c>
       <c r="E74" t="n">
-        <v>3.698569568945551</v>
+        <v>1.225319385540698</v>
       </c>
       <c r="F74" t="n">
-        <v>3.724041028071212</v>
+        <v>1.159300396179055</v>
       </c>
       <c r="G74" t="n">
-        <v>0.01378588023105555</v>
+        <v>0.02674144036354358</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.847648369110399</v>
+        <v>2.468789581418591</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J74" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.02550230826612432</v>
+        <v>0.04004417714781017</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.03532648238034097</v>
+        <v>0.0172474115051191</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.02578008604390209</v>
+        <v>-0.03996481206844509</v>
       </c>
       <c r="P74" t="n">
-        <v>0.03560426015811875</v>
+        <v>0.0172474115051191</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.009824174114216658</v>
+        <v>-0.02271740056332598</v>
       </c>
       <c r="R74" t="n">
-        <v>114.5783003206636</v>
+        <v>116.0449621596877</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55.54917526245117</v>
+        <v>212.9218444824219</v>
       </c>
       <c r="B75" t="n">
-        <v>1.431825041770935</v>
+        <v>349.5711975097656</v>
       </c>
       <c r="C75" t="n">
-        <v>4.01726866921487</v>
+        <v>5.360925171062553</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3589498835399077</v>
+        <v>5.85670725340159</v>
       </c>
       <c r="E75" t="n">
-        <v>3.703586957935786</v>
+        <v>1.210444553657257</v>
       </c>
       <c r="F75" t="n">
-        <v>3.723938698891453</v>
+        <v>1.163339376578618</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01393647879017279</v>
+        <v>0.02809587503466301</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.460321596443553</v>
+        <v>1.676586937424932</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>0.009315134463107277</v>
+        <v>-0.01588104908680843</v>
       </c>
       <c r="N75" t="n">
-        <v>0.004880493787002171</v>
+        <v>-0.001598436271037063</v>
       </c>
       <c r="O75" t="n">
-        <v>0.009235769383742197</v>
+        <v>0.01596041416617351</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.004880493787002171</v>
+        <v>-0.001598436271037063</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004355275596740026</v>
+        <v>0.01436197789513645</v>
       </c>
       <c r="R75" t="n">
-        <v>115.0773203959661</v>
+        <v>117.7115973410671</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>55.56855392456055</v>
+        <v>209.0064086914062</v>
       </c>
       <c r="B76" t="n">
-        <v>1.430027961730957</v>
+        <v>349.7311096191406</v>
       </c>
       <c r="C76" t="n">
-        <v>4.0176174643612</v>
+        <v>5.342364915089938</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3576939977386576</v>
+        <v>5.857164600990844</v>
       </c>
       <c r="E76" t="n">
-        <v>3.70503325561763</v>
+        <v>1.191560188552583</v>
       </c>
       <c r="F76" t="n">
-        <v>3.722762870444613</v>
+        <v>1.165491607379931</v>
       </c>
       <c r="G76" t="n">
-        <v>0.01450732162715705</v>
+        <v>0.02854563548421038</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.222114962543783</v>
+        <v>0.9132247620506355</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0.000348855982430285</v>
+        <v>-0.01838907511126164</v>
       </c>
       <c r="N76" t="n">
-        <v>-0.001255097506714486</v>
+        <v>0.0004574521886075988</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0001984126984126984</v>
+        <v>0.01846844019062672</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>0.0004574521886075988</v>
       </c>
       <c r="Q76" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>0.01892589237923432</v>
       </c>
       <c r="R76" t="n">
-        <v>115.0681872752998</v>
+        <v>119.9393943641319</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>56.23464965820312</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="B77" t="n">
-        <v>1.439061999320984</v>
+        <v>384.5702819824219</v>
       </c>
       <c r="C77" t="n">
-        <v>4.029533108876645</v>
+        <v>5.2950002560248</v>
       </c>
       <c r="D77" t="n">
-        <v>0.363991511981257</v>
+        <v>5.952126560232704</v>
       </c>
       <c r="E77" t="n">
-        <v>3.711445582998823</v>
+        <v>1.076898709931499</v>
       </c>
       <c r="F77" t="n">
-        <v>3.721659650311644</v>
+        <v>1.162716238717049</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01448597116552934</v>
+        <v>0.03409137021669411</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.7051006243286451</v>
+        <v>-2.517280128081377</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01198691861852064</v>
+        <v>-0.04626045560032954</v>
       </c>
       <c r="N77" t="n">
-        <v>0.006317385276223275</v>
+        <v>0.09961702406520634</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>0.04633982067969462</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>0.09961702406520634</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>0.1459568447449009</v>
       </c>
       <c r="R77" t="n">
-        <v>115.0681872752998</v>
+        <v>137.445369926135</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>56.51952362060547</v>
+        <v>198.2189788818359</v>
       </c>
       <c r="B78" t="n">
-        <v>1.43367600440979</v>
+        <v>385.4597778320312</v>
       </c>
       <c r="C78" t="n">
-        <v>4.034586129270641</v>
+        <v>5.289372373526669</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3602417783020882</v>
+        <v>5.954436849899731</v>
       </c>
       <c r="E78" t="n">
-        <v>3.71977544768574</v>
+        <v>1.069633591343409</v>
       </c>
       <c r="F78" t="n">
-        <v>3.72111503900999</v>
+        <v>1.158919659604525</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01433343084502983</v>
+        <v>0.03984453266982312</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.09345922401504281</v>
+        <v>-2.24086122432396</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M78" t="n">
-        <v>0.005065808431879981</v>
+        <v>-0.00561207563438304</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.003742712206795229</v>
+        <v>0.002312960442559797</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>-0.006088266110573517</v>
       </c>
       <c r="P78" t="n">
-        <v>-0</v>
+        <v>-0.001757404887004242</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>-0.007845670997577759</v>
       </c>
       <c r="R78" t="n">
-        <v>115.0681872752998</v>
+        <v>136.3670187735542</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>55.54992294311523</v>
+        <v>198.2489318847656</v>
       </c>
       <c r="B79" t="n">
-        <v>1.400905966758728</v>
+        <v>383.0212097167969</v>
       </c>
       <c r="C79" t="n">
-        <v>4.017282128922035</v>
+        <v>5.289523472781733</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3371191464433027</v>
+        <v>5.948090365497994</v>
       </c>
       <c r="E79" t="n">
-        <v>3.722678019517101</v>
+        <v>1.074282262247248</v>
       </c>
       <c r="F79" t="n">
-        <v>3.720390234516217</v>
+        <v>1.155787083523487</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01383652658616847</v>
+        <v>0.04391858408422406</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1653438806796164</v>
+        <v>-1.855816233053739</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.01715514596334544</v>
+        <v>0.0001511106711307164</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.02285735239361331</v>
+        <v>-0.006326388005902461</v>
       </c>
       <c r="O79" t="n">
-        <v>-0</v>
+        <v>7.174559176563705e-05</v>
       </c>
       <c r="P79" t="n">
-        <v>-0</v>
+        <v>0.006326388005902461</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0</v>
+        <v>0.006398133597668098</v>
       </c>
       <c r="R79" t="n">
-        <v>115.0681872752998</v>
+        <v>137.2395131779831</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>55.71846389770508</v>
+        <v>196.271240234375</v>
       </c>
       <c r="B80" t="n">
-        <v>1.380664944648743</v>
+        <v>388.1981201171875</v>
       </c>
       <c r="C80" t="n">
-        <v>4.020311580292274</v>
+        <v>5.279497581299651</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3225652270679593</v>
+        <v>5.961515828160556</v>
       </c>
       <c r="E80" t="n">
-        <v>3.738425954845193</v>
+        <v>1.054742130057933</v>
       </c>
       <c r="F80" t="n">
-        <v>3.720827081678084</v>
+        <v>1.152188464496217</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01427648625308067</v>
+        <v>0.04907237698590421</v>
       </c>
       <c r="H80" t="n">
-        <v>1.232717410652228</v>
+        <v>-1.985767562599925</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.003034044795389379</v>
+        <v>-0.009975799776516192</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.01444852302029731</v>
+        <v>0.01351598885142269</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>-0.01005516485588127</v>
       </c>
       <c r="P80" t="n">
-        <v>-0</v>
+        <v>-0.01351598885142269</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>-0.02357115370730396</v>
       </c>
       <c r="R80" t="n">
-        <v>115.0681872752998</v>
+        <v>134.0046195181493</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>55.30350875854492</v>
+        <v>207.5880584716797</v>
       </c>
       <c r="B81" t="n">
-        <v>1.36925196647644</v>
+        <v>397.8023986816406</v>
       </c>
       <c r="C81" t="n">
-        <v>4.012836356037061</v>
+        <v>5.335555627824572</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3142645808511502</v>
+        <v>5.98595539627007</v>
       </c>
       <c r="E81" t="n">
-        <v>3.738204559130982</v>
+        <v>1.093480554934123</v>
       </c>
       <c r="F81" t="n">
-        <v>3.721160631248019</v>
+        <v>1.150771450531364</v>
       </c>
       <c r="G81" t="n">
-        <v>0.01461373886313673</v>
+        <v>0.05038699319613187</v>
       </c>
       <c r="H81" t="n">
-        <v>1.166294816308511</v>
+        <v>-1.137017550823782</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.007447354254452976</v>
+        <v>0.05765907538868587</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.008266290975618151</v>
+        <v>0.02474066222050175</v>
       </c>
       <c r="O81" t="n">
-        <v>-0</v>
+        <v>0.05757971030932078</v>
       </c>
       <c r="P81" t="n">
-        <v>-0</v>
+        <v>-0.02474066222050175</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0</v>
+        <v>0.03283904808881903</v>
       </c>
       <c r="R81" t="n">
-        <v>115.0681872752998</v>
+        <v>138.4052036626297</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>55.17010116577148</v>
+        <v>211.2537841796875</v>
       </c>
       <c r="B82" t="n">
-        <v>1.367429971694946</v>
+        <v>397.7524108886719</v>
       </c>
       <c r="C82" t="n">
-        <v>4.010421160992491</v>
+        <v>5.35306017935347</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3129330450045626</v>
+        <v>5.985829728516112</v>
       </c>
       <c r="E82" t="n">
-        <v>3.736952976228776</v>
+        <v>1.111074163599475</v>
       </c>
       <c r="F82" t="n">
-        <v>3.721779679331198</v>
+        <v>1.149864505888023</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01502237300076424</v>
+        <v>0.05095549753252662</v>
       </c>
       <c r="H82" t="n">
-        <v>1.010046608269282</v>
+        <v>-0.7612592196511776</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.002412280807640887</v>
+        <v>0.01765865404299216</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.001330649746067336</v>
+        <v>-0.0001256598580964274</v>
       </c>
       <c r="O82" t="n">
-        <v>-0</v>
+        <v>0.01757928896362708</v>
       </c>
       <c r="P82" t="n">
-        <v>-0</v>
+        <v>0.0001256598580964274</v>
       </c>
       <c r="Q82" t="n">
-        <v>-0</v>
+        <v>0.01770494882172351</v>
       </c>
       <c r="R82" t="n">
-        <v>115.0681872752998</v>
+        <v>140.8556607101368</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>55.3950080871582</v>
+        <v>214.9494781494141</v>
       </c>
       <c r="B83" t="n">
-        <v>1.384695053100586</v>
+        <v>400.5607299804688</v>
       </c>
       <c r="C83" t="n">
-        <v>4.014489482963387</v>
+        <v>5.370403015162717</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3254799371297837</v>
+        <v>5.992865390419841</v>
       </c>
       <c r="E83" t="n">
-        <v>3.730056729680356</v>
+        <v>1.123431027411388</v>
       </c>
       <c r="F83" t="n">
-        <v>3.722558376442162</v>
+        <v>1.148169017524124</v>
       </c>
       <c r="G83" t="n">
-        <v>0.01502786826745102</v>
+        <v>0.05125690306334122</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4989631998861075</v>
+        <v>-0.482627483017576</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.004076608826779848</v>
+        <v>0.01749409594756934</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0126259346094626</v>
+        <v>0.007060470320022549</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>0.01741473086820427</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>-0.007060470320022549</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>0.01035426054818172</v>
       </c>
       <c r="R83" t="n">
-        <v>115.0681872752998</v>
+        <v>142.3141169208158</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>54.94844818115234</v>
+        <v>219.1845397949219</v>
       </c>
       <c r="B84" t="n">
-        <v>1.391958951950073</v>
+        <v>388.4080200195312</v>
       </c>
       <c r="C84" t="n">
-        <v>4.006395439889482</v>
+        <v>5.389914022453838</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3307120729358183</v>
+        <v>5.962056385069926</v>
       </c>
       <c r="E84" t="n">
-        <v>3.717390390058822</v>
+        <v>1.164775494019105</v>
       </c>
       <c r="F84" t="n">
-        <v>3.721575004083618</v>
+        <v>1.148812531655818</v>
       </c>
       <c r="G84" t="n">
-        <v>0.01466832061716528</v>
+        <v>0.05138690485937733</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.2852824214858591</v>
+        <v>0.3106426122953057</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.008061374506945551</v>
+        <v>0.01970259096216065</v>
       </c>
       <c r="N84" t="n">
-        <v>0.005245847331672104</v>
+        <v>-0.03033924459227455</v>
       </c>
       <c r="O84" t="n">
-        <v>-0</v>
+        <v>0.01962322588279557</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.03033924459227455</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>0.04996247047507012</v>
       </c>
       <c r="R84" t="n">
-        <v>115.0681872752998</v>
+        <v>149.4244817856577</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>56.3768310546875</v>
+        <v>220.5229797363281</v>
       </c>
       <c r="B85" t="n">
-        <v>1.413148999214172</v>
+        <v>387.1187744140625</v>
       </c>
       <c r="C85" t="n">
-        <v>4.032058277201147</v>
+        <v>5.396001905948023</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3458205469853537</v>
+        <v>5.958731556573001</v>
       </c>
       <c r="E85" t="n">
-        <v>3.729850125177122</v>
+        <v>1.173219588202269</v>
       </c>
       <c r="F85" t="n">
-        <v>3.721452220816214</v>
+        <v>1.149268558113767</v>
       </c>
       <c r="G85" t="n">
-        <v>0.01458380374480632</v>
+        <v>0.0515698469204601</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5758377243590573</v>
+        <v>0.4644386500786536</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.0259949629300924</v>
+        <v>0.006106452319395217</v>
       </c>
       <c r="N85" t="n">
-        <v>0.01522318401301481</v>
+        <v>-0.003319307375280078</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>-0.005630261843204741</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>-0.003874862930835634</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>-0.009505124774040374</v>
       </c>
       <c r="R85" t="n">
-        <v>115.0681872752998</v>
+        <v>148.0041834419887</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>56.68331146240234</v>
+        <v>225.5671081542969</v>
       </c>
       <c r="B86" t="n">
-        <v>1.424720048904419</v>
+        <v>402.3796691894531</v>
       </c>
       <c r="C86" t="n">
-        <v>4.037479836940898</v>
+        <v>5.418617711806061</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3539753375112478</v>
+        <v>5.997396093626087</v>
       </c>
       <c r="E86" t="n">
-        <v>3.728145317798271</v>
+        <v>1.168434944511359</v>
       </c>
       <c r="F86" t="n">
-        <v>3.721304843008888</v>
+        <v>1.149333736422513</v>
       </c>
       <c r="G86" t="n">
-        <v>0.01449588008943366</v>
+        <v>0.05159442961242068</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4718909612372274</v>
+        <v>0.370218417614754</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0.005436282990392671</v>
+        <v>0.02287348204708572</v>
       </c>
       <c r="N86" t="n">
-        <v>0.008188131397808052</v>
+        <v>0.03942173767854396</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>-0.02279411696772065</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.03942173767854396</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>0.01662762071082331</v>
       </c>
       <c r="R86" t="n">
-        <v>115.0681872752998</v>
+        <v>150.4651408678772</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>56.43155670166016</v>
+        <v>235.465576171875</v>
       </c>
       <c r="B87" t="n">
-        <v>1.387125015258789</v>
+        <v>400.8305969238281</v>
       </c>
       <c r="C87" t="n">
-        <v>4.033028518020188</v>
+        <v>5.46156472940427</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3272332708388891</v>
+        <v>5.993538886487244</v>
       </c>
       <c r="E87" t="n">
-        <v>3.747063548838683</v>
+        <v>1.214115454287753</v>
       </c>
       <c r="F87" t="n">
-        <v>3.721668636175644</v>
+        <v>1.151698041231261</v>
       </c>
       <c r="G87" t="n">
-        <v>0.01506429868361923</v>
+        <v>0.05348708334987745</v>
       </c>
       <c r="H87" t="n">
-        <v>1.685767999983528</v>
+        <v>1.166962360766589</v>
       </c>
       <c r="I87" t="n">
         <v>-1</v>
@@ -5188,54 +5188,54 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.004441426484216193</v>
+        <v>0.04388258597883499</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.02638766379018787</v>
+        <v>-0.003849777670788979</v>
       </c>
       <c r="O87" t="n">
-        <v>-0</v>
+        <v>-0.04380322089946991</v>
       </c>
       <c r="P87" t="n">
-        <v>-0</v>
+        <v>-0.003849777670788979</v>
       </c>
       <c r="Q87" t="n">
-        <v>-0</v>
+        <v>-0.04765299857025888</v>
       </c>
       <c r="R87" t="n">
-        <v>115.0681872752998</v>
+        <v>143.2950257252265</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>58.23315811157227</v>
+        <v>225.0577087402344</v>
       </c>
       <c r="B88" t="n">
-        <v>1.418285012245178</v>
+        <v>396.5431518554688</v>
       </c>
       <c r="C88" t="n">
-        <v>4.064454919507539</v>
+        <v>5.416356852608135</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3494484038545503</v>
+        <v>5.982784867071093</v>
       </c>
       <c r="E88" t="n">
-        <v>3.759076429775691</v>
+        <v>1.176528642915369</v>
       </c>
       <c r="F88" t="n">
-        <v>3.722612156775305</v>
+        <v>1.151942434818453</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01677973822721464</v>
+        <v>0.05359406161049111</v>
       </c>
       <c r="H88" t="n">
-        <v>2.173113341020201</v>
+        <v>0.4587487374180239</v>
       </c>
       <c r="I88" t="n">
         <v>-1</v>
@@ -5250,54 +5250,54 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0.03192542462432391</v>
+        <v>-0.04420122720632225</v>
       </c>
       <c r="N88" t="n">
-        <v>0.02246372651608164</v>
+        <v>-0.01069640167508001</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.03164764684654613</v>
+        <v>0.04428059228568733</v>
       </c>
       <c r="P88" t="n">
-        <v>0.02218594873830386</v>
+        <v>-0.01069640167508001</v>
       </c>
       <c r="Q88" t="n">
-        <v>-0.009461698108242263</v>
+        <v>0.03358419061060731</v>
       </c>
       <c r="R88" t="n">
-        <v>113.9794468254382</v>
+        <v>148.1074731827344</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>58.53215026855469</v>
+        <v>222.0612030029297</v>
       </c>
       <c r="B89" t="n">
-        <v>1.476816058158875</v>
+        <v>396.7030639648438</v>
       </c>
       <c r="C89" t="n">
-        <v>4.069576180515798</v>
+        <v>5.40295303307938</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3898884583252061</v>
+        <v>5.983188051122531</v>
       </c>
       <c r="E89" t="n">
-        <v>3.728857644520461</v>
+        <v>1.162839098401851</v>
       </c>
       <c r="F89" t="n">
-        <v>3.722974764496479</v>
+        <v>1.150963675167325</v>
       </c>
       <c r="G89" t="n">
-        <v>0.01683510701619446</v>
+        <v>0.05318546951417199</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3494412015511895</v>
+        <v>0.2232832264715047</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>-1</v>
@@ -5306,832 +5306,832 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>0.005134397080260866</v>
+        <v>-0.01331438835878007</v>
       </c>
       <c r="N89" t="n">
-        <v>0.04126888841689191</v>
+        <v>0.0004032653410523945</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.005055032000895787</v>
+        <v>0.01339375343814515</v>
       </c>
       <c r="P89" t="n">
-        <v>0.04126888841689191</v>
+        <v>0.0004032653410523945</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.03621385641599613</v>
+        <v>0.01379701877919755</v>
       </c>
       <c r="R89" t="n">
-        <v>118.1070821471493</v>
+        <v>150.1509147715761</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>58.00667190551758</v>
+        <v>220.3531799316406</v>
       </c>
       <c r="B90" t="n">
-        <v>1.436100959777832</v>
+        <v>387.4285888671875</v>
       </c>
       <c r="C90" t="n">
-        <v>4.060558036784399</v>
+        <v>5.395231622459749</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3619317744066359</v>
+        <v>5.959531545016149</v>
       </c>
       <c r="E90" t="n">
-        <v>3.744270489223386</v>
+        <v>1.17188237582652</v>
       </c>
       <c r="F90" t="n">
-        <v>3.723945487503099</v>
+        <v>1.150436593039751</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01749604227238676</v>
+        <v>0.0529087952654414</v>
       </c>
       <c r="H90" t="n">
-        <v>1.161691393050893</v>
+        <v>0.4053349292717108</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.008977602234432447</v>
+        <v>-0.007691677106092865</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.02756951223282433</v>
+        <v>-0.02337888446074154</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.0001984126984126984</v>
+        <v>0.007771042185457944</v>
       </c>
       <c r="P90" t="n">
-        <v>0.0002777777777777778</v>
+        <v>-0.02337888446074154</v>
       </c>
       <c r="Q90" t="n">
-        <v>7.936507936507937e-05</v>
+        <v>-0.0156078422752836</v>
       </c>
       <c r="R90" t="n">
-        <v>118.1164557250975</v>
+        <v>147.8073829763317</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>56.96644973754883</v>
+        <v>223.2098541259766</v>
       </c>
       <c r="B91" t="n">
-        <v>1.426345944404602</v>
+        <v>388.6778564453125</v>
       </c>
       <c r="C91" t="n">
-        <v>4.042462493445287</v>
+        <v>5.408112378842534</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3551158903292142</v>
+        <v>5.962750867995942</v>
       </c>
       <c r="E91" t="n">
-        <v>3.732131259785815</v>
+        <v>1.182481690257254</v>
       </c>
       <c r="F91" t="n">
-        <v>3.724505819667939</v>
+        <v>1.150530165425668</v>
       </c>
       <c r="G91" t="n">
-        <v>0.01757348506943499</v>
+        <v>0.05296659112274621</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4339173526336082</v>
+        <v>0.6032392146502528</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.01793280210357673</v>
+        <v>0.0129640706579417</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.006792708623173049</v>
+        <v>0.00322451056536055</v>
       </c>
       <c r="O91" t="n">
-        <v>-0</v>
+        <v>-0.01288470557857662</v>
       </c>
       <c r="P91" t="n">
-        <v>-0</v>
+        <v>0.00322451056536055</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0</v>
+        <v>-0.009660195013216065</v>
       </c>
       <c r="R91" t="n">
-        <v>118.1164557250975</v>
+        <v>146.3795348323873</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>58.1590576171875</v>
+        <v>219.2544555664062</v>
       </c>
       <c r="B92" t="n">
-        <v>1.484110951423645</v>
+        <v>387.4285888671875</v>
       </c>
       <c r="C92" t="n">
-        <v>4.063181629813169</v>
+        <v>5.390232952899427</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3948159070606901</v>
+        <v>5.959531545016149</v>
       </c>
       <c r="E92" t="n">
-        <v>3.718157059403379</v>
+        <v>1.166883706266199</v>
       </c>
       <c r="F92" t="n">
-        <v>3.725132208662823</v>
+        <v>1.150510114735738</v>
       </c>
       <c r="G92" t="n">
-        <v>0.01708162431751482</v>
+        <v>0.05295999030270203</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.408342270605524</v>
+        <v>0.3091690809774454</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0.02093526777837051</v>
+        <v>-0.01772053736184043</v>
       </c>
       <c r="N92" t="n">
-        <v>0.04049859520100907</v>
+        <v>-0.003214146515961303</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>0.01779990244120551</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-0.003214146515961303</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>0.0145857559252442</v>
       </c>
       <c r="R92" t="n">
-        <v>118.1164557250975</v>
+        <v>148.5145909999032</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>57.49333953857422</v>
+        <v>215.0793304443359</v>
       </c>
       <c r="B93" t="n">
-        <v>1.433730959892273</v>
+        <v>382.7413940429688</v>
       </c>
       <c r="C93" t="n">
-        <v>4.051669106982263</v>
+        <v>5.371006938882586</v>
       </c>
       <c r="D93" t="n">
-        <v>0.360280109437622</v>
+        <v>5.94735954974672</v>
       </c>
       <c r="E93" t="n">
-        <v>3.736824928308379</v>
+        <v>1.15628363653086</v>
       </c>
       <c r="F93" t="n">
-        <v>3.727324812273797</v>
+        <v>1.148415559924708</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01547527981212457</v>
+        <v>0.05179114201370383</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6138897745253599</v>
+        <v>0.1519193495302854</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.01144650731783081</v>
+        <v>-0.01904237298751621</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.03394624336074381</v>
+        <v>-0.01209821618462326</v>
       </c>
       <c r="O93" t="n">
-        <v>-0</v>
+        <v>0.01912173806688129</v>
       </c>
       <c r="P93" t="n">
-        <v>-0</v>
+        <v>-0.01209821618462326</v>
       </c>
       <c r="Q93" t="n">
-        <v>-0</v>
+        <v>0.007023521882258032</v>
       </c>
       <c r="R93" t="n">
-        <v>118.1164557250975</v>
+        <v>149.5576864796257</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>54.31006240844727</v>
+        <v>214.6098785400391</v>
       </c>
       <c r="B94" t="n">
-        <v>1.389199018478394</v>
+        <v>388.6478576660156</v>
       </c>
       <c r="C94" t="n">
-        <v>3.994709521161308</v>
+        <v>5.36882186147656</v>
       </c>
       <c r="D94" t="n">
-        <v>0.32872733535024</v>
+        <v>5.962673683416126</v>
       </c>
       <c r="E94" t="n">
-        <v>3.707438908116487</v>
+        <v>1.143245871391414</v>
       </c>
       <c r="F94" t="n">
-        <v>3.727768279232345</v>
+        <v>1.144311884217244</v>
       </c>
       <c r="G94" t="n">
-        <v>0.01471635918652234</v>
+        <v>0.04852554922789332</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.381413083099798</v>
+        <v>-0.02196807337148494</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.0553677548682171</v>
+        <v>-0.00218269186223996</v>
       </c>
       <c r="N94" t="n">
-        <v>-0.03106017981032194</v>
+        <v>0.01543199589847277</v>
       </c>
       <c r="O94" t="n">
-        <v>-0</v>
+        <v>0.00226205694160504</v>
       </c>
       <c r="P94" t="n">
-        <v>-0</v>
+        <v>0.01543199589847277</v>
       </c>
       <c r="Q94" t="n">
-        <v>-0</v>
+        <v>0.01769405284007781</v>
       </c>
       <c r="R94" t="n">
-        <v>118.1164557250975</v>
+        <v>152.203968086836</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>54.38593673706055</v>
+        <v>212.3525085449219</v>
       </c>
       <c r="B95" t="n">
-        <v>1.360587000846863</v>
+        <v>388.5978698730469</v>
       </c>
       <c r="C95" t="n">
-        <v>3.996105604578054</v>
+        <v>5.358247669945553</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3079162248973413</v>
+        <v>5.962545055387006</v>
       </c>
       <c r="E95" t="n">
-        <v>3.727021554727249</v>
+        <v>1.132762834859047</v>
       </c>
       <c r="F95" t="n">
-        <v>3.728940009071918</v>
+        <v>1.140427798277333</v>
       </c>
       <c r="G95" t="n">
-        <v>0.01357865121572579</v>
+        <v>0.04599655463730506</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.1412846028806639</v>
+        <v>-0.1666421208876613</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M95" t="n">
-        <v>0.001397058394863482</v>
+        <v>-0.01051848130418676</v>
       </c>
       <c r="N95" t="n">
-        <v>-0.02059605373380546</v>
+        <v>-0.0001286197568898251</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>-0.01099467178037723</v>
       </c>
       <c r="P95" t="n">
-        <v>-0</v>
+        <v>0.0006841753124453806</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>-0.01031049646793185</v>
       </c>
       <c r="R95" t="n">
-        <v>118.1164557250975</v>
+        <v>150.6346696114714</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>53.90673065185547</v>
+        <v>214.0005798339844</v>
       </c>
       <c r="B96" t="n">
-        <v>1.365368008613586</v>
+        <v>389.8971252441406</v>
       </c>
       <c r="C96" t="n">
-        <v>3.9872553430662</v>
+        <v>5.365978724522781</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3114239956803794</v>
+        <v>5.965882922901972</v>
       </c>
       <c r="E96" t="n">
-        <v>3.715105897202038</v>
+        <v>1.138128438368819</v>
       </c>
       <c r="F96" t="n">
-        <v>3.729443641151138</v>
+        <v>1.137756210768145</v>
       </c>
       <c r="G96" t="n">
-        <v>0.01281034223013031</v>
+        <v>0.04439416501244557</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.119231921484277</v>
+        <v>0.008384606413237619</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.008811213228189785</v>
+        <v>0.007761016341909066</v>
       </c>
       <c r="N96" t="n">
-        <v>0.003513930210819138</v>
+        <v>0.0033434443979794</v>
       </c>
       <c r="O96" t="n">
-        <v>-0</v>
+        <v>0.007681651262543987</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>-0.0033434443979794</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>0.004338206864564586</v>
       </c>
       <c r="R96" t="n">
-        <v>118.1164557250975</v>
+        <v>151.2881539692213</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>54.13165664672852</v>
+        <v>210.8942108154297</v>
       </c>
       <c r="B97" t="n">
-        <v>1.372087001800537</v>
+        <v>380.1129455566406</v>
       </c>
       <c r="C97" t="n">
-        <v>3.991419165305067</v>
+        <v>5.351356637204843</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3163329396842748</v>
+        <v>5.940468433706842</v>
       </c>
       <c r="E97" t="n">
-        <v>3.714979856074661</v>
+        <v>1.141516871338433</v>
       </c>
       <c r="F97" t="n">
-        <v>3.72962035480493</v>
+        <v>1.140987118838491</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01257114264409147</v>
+        <v>0.04201987479411851</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.164611614454138</v>
+        <v>0.01260718892040579</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M97" t="n">
-        <v>0.004172502990872795</v>
+        <v>-0.01451570374699229</v>
       </c>
       <c r="N97" t="n">
-        <v>0.004921012609467201</v>
+        <v>-0.02509425962392897</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>-0.01459506882635737</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>0.02509425962392897</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>0.0104991907975716</v>
       </c>
       <c r="R97" t="n">
-        <v>118.1164557250975</v>
+        <v>152.8765571631565</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>52.62189102172852</v>
+        <v>224.0988159179688</v>
       </c>
       <c r="B98" t="n">
-        <v>1.333703994750977</v>
+        <v>376.1453247070312</v>
       </c>
       <c r="C98" t="n">
-        <v>3.963132212285469</v>
+        <v>5.41208709707123</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2879600298812676</v>
+        <v>5.929975570597685</v>
       </c>
       <c r="E98" t="n">
-        <v>3.711487625965135</v>
+        <v>1.209683322636755</v>
       </c>
       <c r="F98" t="n">
-        <v>3.729205963718899</v>
+        <v>1.147989605403159</v>
       </c>
       <c r="G98" t="n">
-        <v>0.01304058075016969</v>
+        <v>0.0411639046311005</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.358707721167545</v>
+        <v>1.498733363282178</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.02789062294643896</v>
+        <v>0.0626124588791841</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.02797417875046704</v>
+        <v>-0.01043800506136183</v>
       </c>
       <c r="O98" t="n">
-        <v>-0</v>
+        <v>0.06253309379981901</v>
       </c>
       <c r="P98" t="n">
-        <v>-0</v>
+        <v>0.01043800506136183</v>
       </c>
       <c r="Q98" t="n">
-        <v>-0</v>
+        <v>0.07297109886118085</v>
       </c>
       <c r="R98" t="n">
-        <v>118.1164557250975</v>
+        <v>164.0321275294662</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>51.85989761352539</v>
+        <v>222.5606079101562</v>
       </c>
       <c r="B99" t="n">
-        <v>1.327661037445068</v>
+        <v>361.6340026855469</v>
       </c>
       <c r="C99" t="n">
-        <v>3.948545805822518</v>
+        <v>5.405199459615311</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2834187755864825</v>
+        <v>5.890632658072621</v>
       </c>
       <c r="E99" t="n">
-        <v>3.700869763535389</v>
+        <v>1.230676879989183</v>
       </c>
       <c r="F99" t="n">
-        <v>3.728115550919814</v>
+        <v>1.155809336290255</v>
       </c>
       <c r="G99" t="n">
-        <v>0.01445068631337227</v>
+        <v>0.04127974077177707</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.885432068317229</v>
+        <v>1.813663126249919</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J99" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.01448054019739586</v>
+        <v>-0.006863972045151545</v>
       </c>
       <c r="N99" t="n">
-        <v>-0.004530958390835838</v>
+        <v>-0.03857903067859958</v>
       </c>
       <c r="O99" t="n">
-        <v>-0</v>
+        <v>0.007340162521342022</v>
       </c>
       <c r="P99" t="n">
-        <v>-0</v>
+        <v>-0.03913458623415513</v>
       </c>
       <c r="Q99" t="n">
-        <v>-0</v>
+        <v>-0.03179442371281311</v>
       </c>
       <c r="R99" t="n">
-        <v>118.1164557250975</v>
+        <v>158.8168205642802</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>51.9226188659668</v>
+        <v>214.5</v>
       </c>
       <c r="B100" t="n">
-        <v>1.306151032447815</v>
+        <v>358.7756958007812</v>
       </c>
       <c r="C100" t="n">
-        <v>3.949754511531441</v>
+        <v>5.368309738368072</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2670846692274476</v>
+        <v>5.882697390434339</v>
       </c>
       <c r="E100" t="n">
-        <v>3.716352635833773</v>
+        <v>1.199410655546822</v>
       </c>
       <c r="F100" t="n">
-        <v>3.727011884969243</v>
+        <v>1.1630427625647</v>
       </c>
       <c r="G100" t="n">
-        <v>0.01446470210952764</v>
+        <v>0.03480499715895827</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.7369145285369205</v>
+        <v>1.044904351407538</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>0.001209436488070592</v>
+        <v>-0.03621758578863232</v>
       </c>
       <c r="N100" t="n">
-        <v>-0.01620142821894277</v>
+        <v>-0.007903866515702074</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0009316587102928145</v>
+        <v>0.0362969508679974</v>
       </c>
       <c r="P100" t="n">
-        <v>0.01647920599672055</v>
+        <v>-0.007903866515702074</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.01741086470701336</v>
+        <v>0.02839308435229533</v>
       </c>
       <c r="R100" t="n">
-        <v>120.1729653553991</v>
+        <v>163.3261199471251</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>51.58763885498047</v>
+        <v>218.6600036621094</v>
       </c>
       <c r="B101" t="n">
-        <v>1.31352698802948</v>
+        <v>371.9678344726562</v>
       </c>
       <c r="C101" t="n">
-        <v>3.943282086715116</v>
+        <v>5.3875180287543</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2727158765859599</v>
+        <v>5.918807384063352</v>
       </c>
       <c r="E101" t="n">
-        <v>3.704959170945321</v>
+        <v>1.193028828113042</v>
       </c>
       <c r="F101" t="n">
-        <v>3.72534961555996</v>
+        <v>1.168020176223646</v>
       </c>
       <c r="G101" t="n">
-        <v>0.01501071193721563</v>
+        <v>0.03127226716525897</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.358392906340824</v>
+        <v>0.7997070297857722</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.006451523792569969</v>
+        <v>0.01939395646671027</v>
       </c>
       <c r="N101" t="n">
-        <v>0.005647092410011822</v>
+        <v>0.03676987830078726</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0001984126984126984</v>
+        <v>-0.01931459138734519</v>
       </c>
       <c r="P101" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>0.03676987830078726</v>
       </c>
       <c r="Q101" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>0.01745528691344207</v>
       </c>
       <c r="R101" t="n">
-        <v>120.1634278184661</v>
+        <v>166.1770242312614</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>51.83048248291016</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="B102" t="n">
-        <v>1.328326940536499</v>
+        <v>368.3099975585938</v>
       </c>
       <c r="C102" t="n">
-        <v>3.947978441108898</v>
+        <v>5.323497694837065</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2839202109174432</v>
+        <v>5.908924968232186</v>
       </c>
       <c r="E102" t="n">
-        <v>3.699864200900765</v>
+        <v>1.136011879133064</v>
       </c>
       <c r="F102" t="n">
-        <v>3.723495176793559</v>
+        <v>1.169267062000325</v>
       </c>
       <c r="G102" t="n">
-        <v>0.01577339115685032</v>
+        <v>0.02931833217190074</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.498154433489156</v>
+        <v>-1.134279490125075</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>0.004707399549964908</v>
+        <v>-0.06201407359138122</v>
       </c>
       <c r="N102" t="n">
-        <v>0.01126733797013313</v>
+        <v>-0.009833745219524848</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>0.06209343867074631</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>-0.009833745219524848</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>0.05225969345122146</v>
       </c>
       <c r="R102" t="n">
-        <v>120.1634278184661</v>
+        <v>174.8613845762233</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>50.72057342529297</v>
+        <v>208.6399993896484</v>
       </c>
       <c r="B103" t="n">
-        <v>1.294878959655762</v>
+        <v>363.3099975585938</v>
       </c>
       <c r="C103" t="n">
-        <v>3.926331615768787</v>
+        <v>5.340610275812907</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2584172233358588</v>
+        <v>5.895256457589491</v>
       </c>
       <c r="E103" t="n">
-        <v>3.700504110155545</v>
+        <v>1.16281094195557</v>
       </c>
       <c r="F103" t="n">
-        <v>3.722017545817319</v>
+        <v>1.171236057727534</v>
       </c>
       <c r="G103" t="n">
-        <v>0.01649412145038581</v>
+        <v>0.02733315700102877</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.304309279308154</v>
+        <v>-0.308237931375709</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M103" t="n">
-        <v>-0.02141421427020584</v>
+        <v>0.01725983998433511</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.025180533391296</v>
+        <v>-0.01357552071120349</v>
       </c>
       <c r="O103" t="n">
-        <v>-0</v>
+        <v>0.01678364950814464</v>
       </c>
       <c r="P103" t="n">
-        <v>-0</v>
+        <v>0.01413107626675905</v>
       </c>
       <c r="Q103" t="n">
-        <v>-0</v>
+        <v>0.03091472577490369</v>
       </c>
       <c r="R103" t="n">
-        <v>120.1634278184661</v>
+        <v>180.2671763290172</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>46.90711212158203</v>
+        <v>208.1900024414062</v>
       </c>
       <c r="B104" t="n">
-        <v>1.209893941879272</v>
+        <v>364.260009765625</v>
       </c>
       <c r="C104" t="n">
-        <v>3.848169308338798</v>
+        <v>5.3384511360145</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1905327044276023</v>
+        <v>5.897867925179888</v>
       </c>
       <c r="E104" t="n">
-        <v>3.681665215371633</v>
+        <v>1.158801129902608</v>
       </c>
       <c r="F104" t="n">
-        <v>3.720231287082959</v>
+        <v>1.17093733952171</v>
       </c>
       <c r="G104" t="n">
-        <v>0.01879550674558642</v>
+        <v>0.02743991700200881</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.051877197744733</v>
+        <v>-0.4422830294352884</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -6140,60 +6140,60 @@
         <v>-1</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.07518568987252949</v>
+        <v>-0.002156810532777054</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.0656316307734911</v>
+        <v>0.002614880442088685</v>
       </c>
       <c r="O104" t="n">
-        <v>-0</v>
+        <v>-0.002236175612142133</v>
       </c>
       <c r="P104" t="n">
-        <v>-0</v>
+        <v>-0.002614880442088685</v>
       </c>
       <c r="Q104" t="n">
-        <v>-0</v>
+        <v>-0.004851056054230818</v>
       </c>
       <c r="R104" t="n">
-        <v>120.1634278184661</v>
+        <v>179.3926901519073</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>47.14355087280273</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="B105" t="n">
-        <v>1.20025098323822</v>
+        <v>356.3800048828125</v>
       </c>
       <c r="C105" t="n">
-        <v>3.853197220780635</v>
+        <v>5.300415155494095</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1825306876230951</v>
+        <v>5.875997591000409</v>
       </c>
       <c r="E105" t="n">
-        <v>3.693685987931344</v>
+        <v>1.136264028561349</v>
       </c>
       <c r="F105" t="n">
-        <v>3.71842308022067</v>
+        <v>1.169089561539664</v>
       </c>
       <c r="G105" t="n">
-        <v>0.01954601725789772</v>
+        <v>0.02850187068741539</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.265582239232433</v>
+        <v>-1.151697491660009</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -6202,48 +6202,48 @@
         <v>-1</v>
       </c>
       <c r="M105" t="n">
-        <v>0.00504057360444321</v>
+        <v>-0.03732169739825886</v>
       </c>
       <c r="N105" t="n">
-        <v>-0.007970085895358969</v>
+        <v>-0.02163291240200294</v>
       </c>
       <c r="O105" t="n">
-        <v>0.004762795826665433</v>
+        <v>-0.03740106247762394</v>
       </c>
       <c r="P105" t="n">
-        <v>0.008247863673136747</v>
+        <v>0.02163291240200294</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.01301065949980218</v>
+        <v>-0.015768150075621</v>
       </c>
       <c r="R105" t="n">
-        <v>121.7268332621413</v>
+        <v>176.5639992911226</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>45.55448532104492</v>
+        <v>204.8699951171875</v>
       </c>
       <c r="B106" t="n">
-        <v>1.166646957397461</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="C106" t="n">
-        <v>3.818909089133498</v>
+        <v>5.322375607807396</v>
       </c>
       <c r="D106" t="n">
-        <v>0.1541337860252396</v>
+        <v>5.879890291127706</v>
       </c>
       <c r="E106" t="n">
-        <v>3.684213545316875</v>
+        <v>1.155465835832535</v>
       </c>
       <c r="F106" t="n">
-        <v>3.716226491596601</v>
+        <v>1.168441106105722</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0208227600241271</v>
+        <v>0.02866461555247627</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.537401681747863</v>
+        <v>-0.4526580951149872</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -6252,60 +6252,60 @@
         <v>-1</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.0337069550837451</v>
+        <v>0.02220335789291372</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.02799749911480787</v>
+        <v>0.003900286525099661</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0001984126984126984</v>
+        <v>0.02212399281354864</v>
       </c>
       <c r="P106" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>-0.003900286525099661</v>
       </c>
       <c r="Q106" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>0.01822370628844898</v>
       </c>
       <c r="R106" t="n">
-        <v>121.7171724023586</v>
+        <v>179.7816497553179</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>43.24155426025391</v>
+        <v>205.1900024414062</v>
       </c>
       <c r="B107" t="n">
-        <v>1.096436023712158</v>
+        <v>359.6799926757812</v>
       </c>
       <c r="C107" t="n">
-        <v>3.766801937089247</v>
+        <v>5.323936391063928</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0920649412658727</v>
+        <v>5.885214726902118</v>
       </c>
       <c r="E107" t="n">
-        <v>3.686347562678295</v>
+        <v>1.153253344017569</v>
       </c>
       <c r="F107" t="n">
-        <v>3.713190692288581</v>
+        <v>1.165398000592213</v>
       </c>
       <c r="G107" t="n">
-        <v>0.02051400562723117</v>
+        <v>0.02672556013171084</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.308526969235754</v>
+        <v>-0.454421030458922</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K107" t="n">
         <v>1</v>
@@ -6314,104 +6314,104 @@
         <v>-1</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.05077285023616551</v>
+        <v>0.001562001912655431</v>
       </c>
       <c r="N107" t="n">
-        <v>-0.06018181699280156</v>
+        <v>0.005338635773713296</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.05105062801394329</v>
+        <v>0.001482636833290352</v>
       </c>
       <c r="P107" t="n">
-        <v>0.06045959477057934</v>
+        <v>-0.005338635773713296</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.00940896675663605</v>
+        <v>-0.003855998940422945</v>
       </c>
       <c r="R107" t="n">
-        <v>122.8624052312041</v>
+        <v>179.0884119043539</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>43.06399536132812</v>
+        <v>212.4499969482422</v>
       </c>
       <c r="B108" t="n">
-        <v>1.168192982673645</v>
+        <v>369.3500061035156</v>
       </c>
       <c r="C108" t="n">
-        <v>3.762687273542881</v>
+        <v>5.358706652196227</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1554580956497256</v>
+        <v>5.911744720499765</v>
       </c>
       <c r="E108" t="n">
-        <v>3.626834432486947</v>
+        <v>1.169222558854963</v>
       </c>
       <c r="F108" t="n">
-        <v>3.706578592424143</v>
+        <v>1.165032696389193</v>
       </c>
       <c r="G108" t="n">
-        <v>0.02562191652354684</v>
+        <v>0.02661511524133806</v>
       </c>
       <c r="H108" t="n">
-        <v>-3.112341727595216</v>
+        <v>0.1574241714821622</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J108" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.00410620991690358</v>
+        <v>0.03538181402824003</v>
       </c>
       <c r="N108" t="n">
-        <v>0.0654456415236544</v>
+        <v>0.02688504677670811</v>
       </c>
       <c r="O108" t="n">
-        <v>0.0001984126984126984</v>
+        <v>0.03530244894887495</v>
       </c>
       <c r="P108" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>-0.02688504677670811</v>
       </c>
       <c r="Q108" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>0.008417402172166841</v>
       </c>
       <c r="R108" t="n">
-        <v>122.8526542466619</v>
+        <v>180.5958710917275</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>43.00632858276367</v>
+        <v>207.4100036621094</v>
       </c>
       <c r="B109" t="n">
-        <v>1.137251973152161</v>
+        <v>373.25</v>
       </c>
       <c r="C109" t="n">
-        <v>3.761347281207528</v>
+        <v>5.334697528297165</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1286148024870566</v>
+        <v>5.9222484364193</v>
       </c>
       <c r="E109" t="n">
-        <v>3.648952450647635</v>
+        <v>1.137769752448219</v>
       </c>
       <c r="F109" t="n">
-        <v>3.702583332730502</v>
+        <v>1.163779229091511</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02807728391965683</v>
+        <v>0.02730524863923257</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.910116457002468</v>
+        <v>-0.9525449479306901</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -6420,54 +6420,54 @@
         <v>-1</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L109" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.001339094946499975</v>
+        <v>-0.02372319773372689</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.02648621416186703</v>
+        <v>0.01055907359425179</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.001616872724277752</v>
+        <v>0.02419938820991736</v>
       </c>
       <c r="P109" t="n">
-        <v>0.0267639919396448</v>
+        <v>0.01000351803869623</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.02514711921536705</v>
+        <v>0.03420290624861359</v>
       </c>
       <c r="R109" t="n">
-        <v>125.942044588927</v>
+        <v>186.7727747395646</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>41.71865463256836</v>
+        <v>204.6499938964844</v>
       </c>
       <c r="B110" t="n">
-        <v>1.09723699092865</v>
+        <v>363.7900085449219</v>
       </c>
       <c r="C110" t="n">
-        <v>3.730948382071102</v>
+        <v>5.321301173114246</v>
       </c>
       <c r="D110" t="n">
-        <v>0.09279519344725082</v>
+        <v>5.896576801564275</v>
       </c>
       <c r="E110" t="n">
-        <v>3.649855849620758</v>
+        <v>1.142566149313986</v>
       </c>
       <c r="F110" t="n">
-        <v>3.697862600750371</v>
+        <v>1.162313417765884</v>
       </c>
       <c r="G110" t="n">
-        <v>0.02863105217458898</v>
+        <v>0.02763228200907108</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.676737230503208</v>
+        <v>-0.7146448652129203</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -6482,48 +6482,48 @@
         <v>-1</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.02994149913813837</v>
+        <v>-0.01330702336865741</v>
       </c>
       <c r="N110" t="n">
-        <v>-0.0351856784320187</v>
+        <v>-0.0253449201743553</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.03002086421750345</v>
+        <v>-0.01378321384484789</v>
       </c>
       <c r="P110" t="n">
-        <v>0.0351856784320187</v>
+        <v>0.02590047572991086</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.005164814214515246</v>
+        <v>0.01211726188506297</v>
       </c>
       <c r="R110" t="n">
-        <v>126.592511851025</v>
+        <v>189.0359493640838</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>42.50842666625977</v>
+        <v>210.6900024414062</v>
       </c>
       <c r="B111" t="n">
-        <v>1.141585946083069</v>
+        <v>368.0299987792969</v>
       </c>
       <c r="C111" t="n">
-        <v>3.74970233077681</v>
+        <v>5.350387870426709</v>
       </c>
       <c r="D111" t="n">
-        <v>0.1324184763856063</v>
+        <v>5.908164453268487</v>
       </c>
       <c r="E111" t="n">
-        <v>3.633983518256321</v>
+        <v>1.163441009886336</v>
       </c>
       <c r="F111" t="n">
-        <v>3.692955213673896</v>
+        <v>1.161361383747339</v>
       </c>
       <c r="G111" t="n">
-        <v>0.03077896842914487</v>
+        <v>0.02722586042795039</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.915973745297272</v>
+        <v>0.07638422096890977</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -6538,54 +6538,54 @@
         <v>-1</v>
       </c>
       <c r="M111" t="n">
-        <v>0.01893090850237678</v>
+        <v>0.02951384668976353</v>
       </c>
       <c r="N111" t="n">
-        <v>0.04041875686025143</v>
+        <v>0.0116550486126159</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0188515434230117</v>
+        <v>0.02943448161039846</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.04041875686025143</v>
+        <v>-0.0116550486126159</v>
       </c>
       <c r="Q111" t="n">
-        <v>-0.02156721343723973</v>
+        <v>0.01777943299778255</v>
       </c>
       <c r="R111" t="n">
-        <v>123.8622641283776</v>
+        <v>192.3969013599747</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>43.04612350463867</v>
+        <v>208.6499938964844</v>
       </c>
       <c r="B112" t="n">
-        <v>1.13205897808075</v>
+        <v>349.6799926757812</v>
       </c>
       <c r="C112" t="n">
-        <v>3.762272180469467</v>
+        <v>5.34065817778515</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1240380792018401</v>
+        <v>5.857018429609569</v>
       </c>
       <c r="E112" t="n">
-        <v>3.653876889839772</v>
+        <v>1.189957038717434</v>
       </c>
       <c r="F112" t="n">
-        <v>3.689741205195715</v>
+        <v>1.1625150503699</v>
       </c>
       <c r="G112" t="n">
-        <v>0.03135949315618153</v>
+        <v>0.02795136617360552</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.143650988787559</v>
+        <v>0.9817762815989773</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
         <v>1</v>
@@ -6594,48 +6594,48 @@
         <v>-1</v>
       </c>
       <c r="M112" t="n">
-        <v>0.01264918230449807</v>
+        <v>-0.009682512322762959</v>
       </c>
       <c r="N112" t="n">
-        <v>-0.008345379544139941</v>
+        <v>-0.04986008250517615</v>
       </c>
       <c r="O112" t="n">
-        <v>0.01256981722513299</v>
+        <v>-0.00976187740212804</v>
       </c>
       <c r="P112" t="n">
-        <v>0.008345379544139941</v>
+        <v>0.04986008250517615</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.02091519676927293</v>
+        <v>0.04009820510304811</v>
       </c>
       <c r="R112" t="n">
-        <v>126.4528677549103</v>
+        <v>200.1116717718978</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>45.8035888671875</v>
+        <v>200.0399932861328</v>
       </c>
       <c r="B113" t="n">
-        <v>1.238212943077087</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="C113" t="n">
-        <v>3.824362447595769</v>
+        <v>5.298517312988079</v>
       </c>
       <c r="D113" t="n">
-        <v>0.213669165187666</v>
+        <v>5.846814441141912</v>
       </c>
       <c r="E113" t="n">
-        <v>3.637639697548718</v>
+        <v>1.155047448171035</v>
       </c>
       <c r="F113" t="n">
-        <v>3.684781943657733</v>
+        <v>1.162453240951909</v>
       </c>
       <c r="G113" t="n">
-        <v>0.03136436380934753</v>
+        <v>0.02796723336949554</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.503051246171478</v>
+        <v>-0.2648024809258331</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -6644,60 +6644,60 @@
         <v>-1</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>0.06405838988618062</v>
+        <v>-0.04126528091164561</v>
       </c>
       <c r="N113" t="n">
-        <v>0.09377070192606696</v>
+        <v>-0.01015210440209613</v>
       </c>
       <c r="O113" t="n">
-        <v>0.0001984126984126984</v>
+        <v>0.04174147138783608</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>-0.01070765995765168</v>
       </c>
       <c r="Q113" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>0.0310338114301844</v>
       </c>
       <c r="R113" t="n">
-        <v>126.442831813025</v>
+        <v>206.3218996586459</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>45.63327026367188</v>
+        <v>199</v>
       </c>
       <c r="B114" t="n">
-        <v>1.215988993644714</v>
+        <v>345.2900085449219</v>
       </c>
       <c r="C114" t="n">
-        <v>3.820637061529032</v>
+        <v>5.293304824724492</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1955577322239944</v>
+        <v>5.84438466839932</v>
       </c>
       <c r="E114" t="n">
-        <v>3.649741661054388</v>
+        <v>1.151556870229493</v>
       </c>
       <c r="F114" t="n">
-        <v>3.681897081304629</v>
+        <v>1.162868790893813</v>
       </c>
       <c r="G114" t="n">
-        <v>0.03182086188968589</v>
+        <v>0.02772753801105472</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.010513805745259</v>
+        <v>-0.4079670059350384</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K114" t="n">
         <v>1</v>
@@ -6706,414 +6706,302 @@
         <v>-1</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.003718455425173794</v>
+        <v>-0.00519892681982459</v>
       </c>
       <c r="N114" t="n">
-        <v>-0.01794840665866748</v>
+        <v>-0.002426823234163211</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.003996233202951572</v>
+        <v>-0.005675117296015066</v>
       </c>
       <c r="P114" t="n">
-        <v>0.01822618443644526</v>
+        <v>0.002982378789718766</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.01422995123349369</v>
+        <v>-0.0026927385062963</v>
       </c>
       <c r="R114" t="n">
-        <v>128.2421071435492</v>
+        <v>205.7663287347429</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>44.86038970947266</v>
+        <v>195.7400054931641</v>
       </c>
       <c r="B115" t="n">
-        <v>1.18508505821228</v>
+        <v>343.7099914550781</v>
       </c>
       <c r="C115" t="n">
-        <v>3.803555216291793</v>
+        <v>5.276787276061247</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1698145510931925</v>
+        <v>5.839798253712797</v>
       </c>
       <c r="E115" t="n">
-        <v>3.65515645248197</v>
+        <v>1.138289582239383</v>
       </c>
       <c r="F115" t="n">
-        <v>3.678303826192364</v>
+        <v>1.16314512826283</v>
       </c>
       <c r="G115" t="n">
-        <v>0.03048674540187209</v>
+        <v>0.02743773101465209</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.7592602426158809</v>
+        <v>-0.9058892665058047</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.0169367777004249</v>
+        <v>-0.01638188194389922</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.02541465062097725</v>
+        <v>-0.004575913147623512</v>
       </c>
       <c r="O115" t="n">
-        <v>0.0001984126984126984</v>
+        <v>-0.0164612470232643</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.0002777777777777778</v>
+        <v>0.004575913147623512</v>
       </c>
       <c r="Q115" t="n">
-        <v>-7.936507936507937e-05</v>
+        <v>-0.01188533387564079</v>
       </c>
       <c r="R115" t="n">
-        <v>128.2319291985378</v>
+        <v>203.3207272173656</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>43.80323028564453</v>
+        <v>192.5299987792969</v>
       </c>
       <c r="B116" t="n">
-        <v>1.145421981811523</v>
+        <v>337.3900146484375</v>
       </c>
       <c r="C116" t="n">
-        <v>3.779707565476745</v>
+        <v>5.260251979400917</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1357731121777207</v>
+        <v>5.821239574678188</v>
       </c>
       <c r="E116" t="n">
-        <v>3.661057179652454</v>
+        <v>1.134906289646365</v>
       </c>
       <c r="F116" t="n">
-        <v>3.675601390314885</v>
+        <v>1.162984020826707</v>
       </c>
       <c r="G116" t="n">
-        <v>0.02943000836204119</v>
+        <v>0.02760132596209426</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.494196620113422</v>
+        <v>-1.017260229414436</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.02356554257942389</v>
+        <v>-0.01639933904047675</v>
       </c>
       <c r="N116" t="n">
-        <v>-0.03346854820749257</v>
+        <v>-0.01838752717046521</v>
       </c>
       <c r="O116" t="n">
-        <v>-0</v>
+        <v>-0.01647870411984182</v>
       </c>
       <c r="P116" t="n">
-        <v>-0</v>
+        <v>0.01838752717046521</v>
       </c>
       <c r="Q116" t="n">
-        <v>-0</v>
+        <v>0.001908823050623388</v>
       </c>
       <c r="R116" t="n">
-        <v>128.2319291985378</v>
+        <v>203.7088305081476</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>44.54055786132812</v>
+        <v>194.9700012207031</v>
       </c>
       <c r="B117" t="n">
-        <v>1.128630995750427</v>
+        <v>353.6499938964844</v>
       </c>
       <c r="C117" t="n">
-        <v>3.796400186702023</v>
+        <v>5.272845706835346</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1210053900694745</v>
+        <v>5.868307706223366</v>
       </c>
       <c r="E117" t="n">
-        <v>3.690655124308749</v>
+        <v>1.114144180904709</v>
       </c>
       <c r="F117" t="n">
-        <v>3.674385153726589</v>
+        <v>1.161615386305021</v>
       </c>
       <c r="G117" t="n">
-        <v>0.02819364352062766</v>
+        <v>0.02934536540994907</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5770793891983662</v>
+        <v>-1.617673003458916</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M117" t="n">
-        <v>0.01683272148824222</v>
+        <v>0.01267336236886019</v>
       </c>
       <c r="N117" t="n">
-        <v>-0.01465921409552551</v>
+        <v>0.04819342168436691</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>0.01259399728949511</v>
       </c>
       <c r="P117" t="n">
-        <v>-0</v>
+        <v>-0.04819342168436691</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>-0.03559942439487181</v>
       </c>
       <c r="R117" t="n">
-        <v>128.2319291985378</v>
+        <v>196.4569133979051</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>42.13380432128906</v>
+        <v>200.0899963378906</v>
       </c>
       <c r="B118" t="n">
-        <v>1.109410047531128</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="C118" t="n">
-        <v>3.740850371493776</v>
+        <v>5.29876724702609</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1038283853233574</v>
+        <v>5.878771645975505</v>
       </c>
       <c r="E118" t="n">
-        <v>3.65011607380747</v>
+        <v>1.132650226817892</v>
       </c>
       <c r="F118" t="n">
-        <v>3.671316576118706</v>
+        <v>1.157763731514078</v>
       </c>
       <c r="G118" t="n">
-        <v>0.02726750580876797</v>
+        <v>0.02771433983582536</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.7775006067631951</v>
+        <v>-0.9061556163687622</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.05403510094175767</v>
+        <v>0.02626042511735815</v>
       </c>
       <c r="N118" t="n">
-        <v>-0.01703032106301428</v>
+        <v>0.01051887822679287</v>
       </c>
       <c r="O118" t="n">
-        <v>-0</v>
+        <v>0.02618106003799308</v>
       </c>
       <c r="P118" t="n">
-        <v>-0</v>
+        <v>-0.01051887822679287</v>
       </c>
       <c r="Q118" t="n">
-        <v>-0</v>
+        <v>0.0156621818112002</v>
       </c>
       <c r="R118" t="n">
-        <v>128.2319291985378</v>
+        <v>199.5338572936103</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>41.02338027954102</v>
+        <v>195.8800048828125</v>
       </c>
       <c r="B119" t="n">
-        <v>1.072260022163391</v>
+        <v>361.875</v>
       </c>
       <c r="C119" t="n">
-        <v>3.714142154893664</v>
+        <v>5.277502251761687</v>
       </c>
       <c r="D119" t="n">
-        <v>0.06976859122441545</v>
+        <v>5.89129884832726</v>
       </c>
       <c r="E119" t="n">
-        <v>3.653172275552912</v>
+        <v>1.102507562190543</v>
       </c>
       <c r="F119" t="n">
-        <v>3.668931701719583</v>
+        <v>1.151355265624146</v>
       </c>
       <c r="G119" t="n">
-        <v>0.02662497128848163</v>
+        <v>0.02461188880953677</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.5919039684932427</v>
+        <v>-1.984719816167663</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.02635470638446435</v>
+        <v>-0.02104048944040526</v>
       </c>
       <c r="N119" t="n">
-        <v>-0.0334862889068025</v>
+        <v>0.01260599643049276</v>
       </c>
       <c r="O119" t="n">
-        <v>-0</v>
+        <v>-0.02111985451977034</v>
       </c>
       <c r="P119" t="n">
-        <v>-0</v>
+        <v>-0.01260599643049276</v>
       </c>
       <c r="Q119" t="n">
-        <v>-0</v>
+        <v>-0.03372585095026311</v>
       </c>
       <c r="R119" t="n">
-        <v>128.2319291985378</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>40.8530387878418</v>
-      </c>
-      <c r="B120" t="n">
-        <v>1.041640996932983</v>
-      </c>
-      <c r="C120" t="n">
-        <v>3.709981207470548</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0.04079735127227685</v>
-      </c>
-      <c r="E120" t="n">
-        <v>3.674328924102921</v>
-      </c>
-      <c r="F120" t="n">
-        <v>3.666830516133039</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0.02423674703067279</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.3093817813253502</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-0.004152302675656694</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-0.02855559714763101</v>
-      </c>
-      <c r="O120" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>128.2319291985378</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>41.84611511230469</v>
-      </c>
-      <c r="B121" t="n">
-        <v>1.04711902141571</v>
-      </c>
-      <c r="C121" t="n">
-        <v>3.733998963768906</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0.04604260395251977</v>
-      </c>
-      <c r="E121" t="n">
-        <v>3.693762921185078</v>
-      </c>
-      <c r="F121" t="n">
-        <v>3.666270703645027</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.02342543663538012</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1.17360534055229</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0.02430850565658371</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0.005259033101477906</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>128.2319291985378</v>
+        <v>192.8044081629949</v>
       </c>
     </row>
   </sheetData>

--- a/Notebooks/trades_taken.xlsx
+++ b/Notebooks/trades_taken.xlsx
@@ -534,7 +534,7 @@
         <v>5.803412276142656</v>
       </c>
       <c r="E2" t="n">
-        <v>1.106100513230704</v>
+        <v>1.10026075413351</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -574,7 +574,7 @@
         <v>5.815721099515246</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1020708121672</v>
+        <v>1.096218667156368</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -624,7 +624,7 @@
         <v>5.815334021863411</v>
       </c>
       <c r="E4" t="n">
-        <v>1.087871361129742</v>
+        <v>1.082019605620832</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -674,7 +674,7 @@
         <v>5.806180751990471</v>
       </c>
       <c r="E5" t="n">
-        <v>1.115483045008688</v>
+        <v>1.109640500096657</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -724,7 +724,7 @@
         <v>5.797791852433679</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11703453020351</v>
+        <v>1.111200426730787</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -774,7 +774,7 @@
         <v>5.773250764797821</v>
       </c>
       <c r="E7" t="n">
-        <v>1.089620468097828</v>
+        <v>1.083811059413785</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>5.792870686585944</v>
       </c>
       <c r="E8" t="n">
-        <v>1.104772929357007</v>
+        <v>1.098943777871436</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -874,7 +874,7 @@
         <v>5.799426904789393</v>
       </c>
       <c r="E9" t="n">
-        <v>1.108383937863929</v>
+        <v>1.102548189098503</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -924,7 +924,7 @@
         <v>5.791499330208546</v>
       </c>
       <c r="E10" t="n">
-        <v>1.129196503110411</v>
+        <v>1.123368731570035</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -974,7 +974,7 @@
         <v>5.807622181149471</v>
       </c>
       <c r="E11" t="n">
-        <v>1.111355999905367</v>
+        <v>1.105512004536495</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         <v>5.811485489879658</v>
       </c>
       <c r="E12" t="n">
-        <v>1.119551906398167</v>
+        <v>1.113704023524628</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         <v>5.81584014920781</v>
       </c>
       <c r="E13" t="n">
-        <v>1.132253984661991</v>
+        <v>1.126401719855855</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>5.822484413078896</v>
       </c>
       <c r="E14" t="n">
-        <v>1.13270127562991</v>
+        <v>1.126842324946822</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
         <v>5.821745073183263</v>
       </c>
       <c r="E15" t="n">
-        <v>1.126030989391238</v>
+        <v>1.120172782678538</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
         <v>5.838439306937361</v>
       </c>
       <c r="E16" t="n">
-        <v>1.08489405834881</v>
+        <v>1.079019052846226</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
         <v>5.826791450769824</v>
       </c>
       <c r="E17" t="n">
-        <v>1.064344817352811</v>
+        <v>1.058481532657017</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
         <v>5.806961780196065</v>
       </c>
       <c r="E18" t="n">
-        <v>1.043700357823711</v>
+        <v>1.037857026991889</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
         <v>5.801572505737814</v>
       </c>
       <c r="E19" t="n">
-        <v>1.034169461351605</v>
+        <v>1.028331553547314</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>5.775917931798511</v>
       </c>
       <c r="E20" t="n">
-        <v>1.12812315790135</v>
+        <v>1.122311065345816</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1474,16 +1474,16 @@
         <v>5.780429907926294</v>
       </c>
       <c r="E21" t="n">
-        <v>1.149590552089203</v>
+        <v>1.143773919298996</v>
       </c>
       <c r="F21" t="n">
-        <v>1.104362533051159</v>
+        <v>1.098520935896075</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02986159584211987</v>
+        <v>0.02986531925980943</v>
       </c>
       <c r="H21" t="n">
-        <v>1.514588144490569</v>
+        <v>1.515235213434273</v>
       </c>
       <c r="I21" t="n">
         <v>-1</v>
@@ -1530,16 +1530,16 @@
         <v>5.762572732764129</v>
       </c>
       <c r="E22" t="n">
-        <v>1.154321049785048</v>
+        <v>1.148522386009645</v>
       </c>
       <c r="F22" t="n">
-        <v>1.106773559878876</v>
+        <v>1.100934017489882</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0318872644354834</v>
+        <v>0.03189412368389612</v>
       </c>
       <c r="H22" t="n">
-        <v>1.491112227653569</v>
+        <v>1.492073241811331</v>
       </c>
       <c r="I22" t="n">
         <v>-1</v>
@@ -1586,16 +1586,16 @@
         <v>5.738363452452096</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1794545784901</v>
+        <v>1.17368027561794</v>
       </c>
       <c r="F23" t="n">
-        <v>1.110642748195021</v>
+        <v>1.104807097912961</v>
       </c>
       <c r="G23" t="n">
-        <v>0.035747769379214</v>
+        <v>0.03576033960843624</v>
       </c>
       <c r="H23" t="n">
-        <v>1.924926547587341</v>
+        <v>1.925965425919256</v>
       </c>
       <c r="I23" t="n">
         <v>-1</v>
@@ -1642,16 +1642,16 @@
         <v>5.732040421829392</v>
       </c>
       <c r="E24" t="n">
-        <v>1.167436017851239</v>
+        <v>1.161668077610897</v>
       </c>
       <c r="F24" t="n">
-        <v>1.114620981031096</v>
+        <v>1.108789521512464</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03746617420077004</v>
+        <v>0.03748258763607924</v>
       </c>
       <c r="H24" t="n">
-        <v>1.409672536542503</v>
+        <v>1.410749882367627</v>
       </c>
       <c r="I24" t="n">
         <v>-1</v>
@@ -1698,16 +1698,16 @@
         <v>5.721368826915722</v>
       </c>
       <c r="E25" t="n">
-        <v>1.152658237915567</v>
+        <v>1.14690103610643</v>
       </c>
       <c r="F25" t="n">
-        <v>1.11647974067644</v>
+        <v>1.110652548312953</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03842118383900175</v>
+        <v>0.03844085624281826</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9416289042713365</v>
+        <v>0.9429677519279803</v>
       </c>
       <c r="I25" t="n">
         <v>-1</v>
@@ -1754,16 +1754,16 @@
         <v>5.70919231456057</v>
       </c>
       <c r="E26" t="n">
-        <v>1.173033727945996</v>
+        <v>1.167288778910814</v>
       </c>
       <c r="F26" t="n">
-        <v>1.119279700563564</v>
+        <v>1.113456965921954</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04045062627938346</v>
+        <v>0.04047504522152102</v>
       </c>
       <c r="H26" t="n">
-        <v>1.328879978548778</v>
+        <v>1.330000070271384</v>
       </c>
       <c r="I26" t="n">
         <v>-1</v>
@@ -1810,16 +1810,16 @@
         <v>5.713520469255783</v>
       </c>
       <c r="E27" t="n">
-        <v>1.186108327067464</v>
+        <v>1.180359022770317</v>
       </c>
       <c r="F27" t="n">
-        <v>1.124104093512046</v>
+        <v>1.118284364089781</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04243242929709501</v>
+        <v>0.04246192499072122</v>
       </c>
       <c r="H27" t="n">
-        <v>1.461246376475134</v>
+        <v>1.461889885917826</v>
       </c>
       <c r="I27" t="n">
         <v>-1</v>
@@ -1866,16 +1866,16 @@
         <v>5.711936800350696</v>
       </c>
       <c r="E28" t="n">
-        <v>1.186805000139769</v>
+        <v>1.181057289430059</v>
       </c>
       <c r="F28" t="n">
-        <v>1.128205697051184</v>
+        <v>1.122390039667712</v>
       </c>
       <c r="G28" t="n">
-        <v>0.04438524933822412</v>
+        <v>0.044418190231811</v>
       </c>
       <c r="H28" t="n">
-        <v>1.320242737447447</v>
+        <v>1.320793338408735</v>
       </c>
       <c r="I28" t="n">
         <v>-1</v>
@@ -1922,16 +1922,16 @@
         <v>5.751208299404545</v>
       </c>
       <c r="E29" t="n">
-        <v>1.169140856245554</v>
+        <v>1.163353628079054</v>
       </c>
       <c r="F29" t="n">
-        <v>1.131243542970266</v>
+        <v>1.125430311616739</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04503166826154525</v>
+        <v>0.04506485870793681</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8415702712850818</v>
+        <v>0.8415274684004752</v>
       </c>
       <c r="I29" t="n">
         <v>-1</v>
@@ -1978,16 +1978,16 @@
         <v>5.740066355466205</v>
       </c>
       <c r="E30" t="n">
-        <v>1.186109355602546</v>
+        <v>1.180333339162075</v>
       </c>
       <c r="F30" t="n">
-        <v>1.134089185594872</v>
+        <v>1.128278541996341</v>
       </c>
       <c r="G30" t="n">
-        <v>0.04666413317054702</v>
+        <v>0.04669826566846543</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1147784491689</v>
+        <v>1.114705148480171</v>
       </c>
       <c r="I30" t="n">
         <v>-1</v>
@@ -2034,16 +2034,16 @@
         <v>5.738170534486693</v>
       </c>
       <c r="E31" t="n">
-        <v>1.194216761405623</v>
+        <v>1.188442652659674</v>
       </c>
       <c r="F31" t="n">
-        <v>1.138232223669885</v>
+        <v>1.1324250744025</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0481928786604718</v>
+        <v>0.04822718313876609</v>
       </c>
       <c r="H31" t="n">
-        <v>1.161676564916566</v>
+        <v>1.161535354366275</v>
       </c>
       <c r="I31" t="n">
         <v>-1</v>
@@ -2090,16 +2090,16 @@
         <v>5.744582789253949</v>
       </c>
       <c r="E32" t="n">
-        <v>1.203627038298979</v>
+        <v>1.197846477138257</v>
       </c>
       <c r="F32" t="n">
-        <v>1.142435980264926</v>
+        <v>1.136632197083182</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0501065252893487</v>
+        <v>0.05014024921811436</v>
       </c>
       <c r="H32" t="n">
-        <v>1.221219345797685</v>
+        <v>1.220861104794037</v>
       </c>
       <c r="I32" t="n">
         <v>-1</v>
@@ -2146,16 +2146,16 @@
         <v>5.726784026444416</v>
       </c>
       <c r="E33" t="n">
-        <v>1.160134347796584</v>
+        <v>1.154371696872476</v>
       </c>
       <c r="F33" t="n">
-        <v>1.143829998421655</v>
+        <v>1.138030695934013</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05019609289747783</v>
+        <v>0.05022987077804231</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3248131165951295</v>
+        <v>0.3253243674599731</v>
       </c>
       <c r="I33" t="n">
         <v>-1</v>
@@ -2202,16 +2202,16 @@
         <v>5.740932893433766</v>
       </c>
       <c r="E34" t="n">
-        <v>1.107569040019739</v>
+        <v>1.101792151614166</v>
       </c>
       <c r="F34" t="n">
-        <v>1.142573386641147</v>
+        <v>1.13677818726738</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05080029748730964</v>
+        <v>0.05083225009209078</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6890579062091517</v>
+        <v>-0.6882645483886874</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2258,16 +2258,16 @@
         <v>5.723982150556365</v>
       </c>
       <c r="E35" t="n">
-        <v>1.14899951085405</v>
+        <v>1.143239679354002</v>
       </c>
       <c r="F35" t="n">
-        <v>1.143721812714287</v>
+        <v>1.137931532101153</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05066608997196639</v>
+        <v>0.05069716210856846</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1041662804981074</v>
+        <v>0.1047030451424721</v>
       </c>
       <c r="I35" t="n">
         <v>-1</v>
@@ -2314,16 +2314,16 @@
         <v>5.714344279418622</v>
       </c>
       <c r="E36" t="n">
-        <v>1.142423562063159</v>
+        <v>1.136673428796319</v>
       </c>
       <c r="F36" t="n">
-        <v>1.146598287900005</v>
+        <v>1.140814250898658</v>
       </c>
       <c r="G36" t="n">
-        <v>0.04874719930907108</v>
+        <v>0.04877366844066616</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08564032182397056</v>
+        <v>-0.08489872168167144</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -2370,16 +2370,16 @@
         <v>5.712861012783621</v>
       </c>
       <c r="E37" t="n">
-        <v>1.159944834991074</v>
+        <v>1.154196194280582</v>
       </c>
       <c r="F37" t="n">
-        <v>1.151378288781918</v>
+        <v>1.145599983979836</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04478311953043168</v>
+        <v>0.04480418156188373</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1912896265150692</v>
+        <v>0.1918617861342391</v>
       </c>
       <c r="I37" t="n">
         <v>-1</v>
@@ -2426,16 +2426,16 @@
         <v>5.705410685348077</v>
       </c>
       <c r="E38" t="n">
-        <v>1.166862242184495</v>
+        <v>1.161121098462902</v>
       </c>
       <c r="F38" t="n">
-        <v>1.157536382999957</v>
+        <v>1.151763187553387</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03698634286514927</v>
+        <v>0.03700180484337991</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2521433172925335</v>
+        <v>0.2529041745159602</v>
       </c>
       <c r="I38" t="n">
         <v>-1</v>
@@ -2482,16 +2482,16 @@
         <v>5.697536098237152</v>
       </c>
       <c r="E39" t="n">
-        <v>1.141872357734086</v>
+        <v>1.136139137918211</v>
       </c>
       <c r="F39" t="n">
-        <v>1.162921527819081</v>
+        <v>1.157153566771932</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02343835166683853</v>
+        <v>0.02344215339812473</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8980652899229359</v>
+        <v>-0.8964376478912423</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2538,16 +2538,16 @@
         <v>5.724163671495992</v>
       </c>
       <c r="E40" t="n">
-        <v>1.149802001589033</v>
+        <v>1.144041987431179</v>
       </c>
       <c r="F40" t="n">
-        <v>1.164005470003465</v>
+        <v>1.1582401128762</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0222136362277263</v>
+        <v>0.02221362611851348</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6394031246763658</v>
+        <v>-0.6391628889975508</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2594,16 +2594,16 @@
         <v>5.726380928450948</v>
       </c>
       <c r="E41" t="n">
-        <v>1.159770744986512</v>
+        <v>1.154008499685003</v>
       </c>
       <c r="F41" t="n">
-        <v>1.164514479648331</v>
+        <v>1.1587518418955</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02198136564386955</v>
+        <v>0.02197948443331438</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2158070949127911</v>
+        <v>-0.2158077103622919</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2650,16 +2650,16 @@
         <v>5.731772886030789</v>
       </c>
       <c r="E42" t="n">
-        <v>1.162799899009847</v>
+        <v>1.157032227980881</v>
       </c>
       <c r="F42" t="n">
-        <v>1.164938422109571</v>
+        <v>1.159177333994062</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02185582844821663</v>
+        <v>0.02185303955361792</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.09784681028178788</v>
+        <v>-0.09816053313395404</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2706,16 +2706,16 @@
         <v>5.714949142745352</v>
       </c>
       <c r="E43" t="n">
-        <v>1.159065386240345</v>
+        <v>1.153314644321915</v>
       </c>
       <c r="F43" t="n">
-        <v>1.163918962497083</v>
+        <v>1.158159052429261</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02161731190045196</v>
+        <v>0.02161486974095401</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2245226547633881</v>
+        <v>-0.2241238631277521</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2762,16 +2762,16 @@
         <v>5.710756593323133</v>
       </c>
       <c r="E44" t="n">
-        <v>1.146130376854661</v>
+        <v>1.140383853743625</v>
       </c>
       <c r="F44" t="n">
-        <v>1.162853680447254</v>
+        <v>1.157094841235897</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02195716270390204</v>
+        <v>0.02195430997819718</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7616331772056054</v>
+        <v>-0.7611711554072004</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -2818,16 +2818,16 @@
         <v>5.721549023996647</v>
       </c>
       <c r="E45" t="n">
-        <v>1.15482498703296</v>
+        <v>1.149067603898165</v>
       </c>
       <c r="F45" t="n">
-        <v>1.162962017903124</v>
+        <v>1.157203169625484</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02190950408473793</v>
+        <v>0.02190665722081511</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.3713927452986963</v>
+        <v>-0.3713741282074201</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2874,16 +2874,16 @@
         <v>5.738938545760967</v>
       </c>
       <c r="E46" t="n">
-        <v>1.135435830510881</v>
+        <v>1.129660948943597</v>
       </c>
       <c r="F46" t="n">
-        <v>1.161082123031368</v>
+        <v>1.155321778127123</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02260190090996305</v>
+        <v>0.02259971204665973</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.134696263940445</v>
+        <v>-1.135449386724323</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -2930,16 +2930,16 @@
         <v>5.728495630575953</v>
       </c>
       <c r="E47" t="n">
-        <v>1.134391064631173</v>
+        <v>1.128626691383142</v>
       </c>
       <c r="F47" t="n">
-        <v>1.158496259909553</v>
+        <v>1.152735161557764</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02254637386938444</v>
+        <v>0.02254369446051803</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.069138452951516</v>
+        <v>-1.069410793197408</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -2986,16 +2986,16 @@
         <v>5.726673971164641</v>
       </c>
       <c r="E48" t="n">
-        <v>1.1254300819972</v>
+        <v>1.119667541817648</v>
       </c>
       <c r="F48" t="n">
-        <v>1.155427514002425</v>
+        <v>1.149665674177144</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02266702199691337</v>
+        <v>0.02266348155899244</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.323395371889162</v>
+        <v>-1.323633012051171</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -3042,16 +3042,16 @@
         <v>5.706513118053733</v>
       </c>
       <c r="E49" t="n">
-        <v>1.106348795718598</v>
+        <v>1.100606542659754</v>
       </c>
       <c r="F49" t="n">
-        <v>1.152287910976077</v>
+        <v>1.146528319906179</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02490572384815192</v>
+        <v>0.02490150386275551</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.844520381642619</v>
+        <v>-1.844136703530912</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>5.710028592673332</v>
       </c>
       <c r="E50" t="n">
-        <v>1.120737980849365</v>
+        <v>1.114992190298454</v>
       </c>
       <c r="F50" t="n">
-        <v>1.149019342238418</v>
+        <v>1.143261262462998</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02452007090885564</v>
+        <v>0.02451625438777132</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.153396394903525</v>
+        <v>-1.153074679248063</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -3154,16 +3154,16 @@
         <v>5.670799921537744</v>
       </c>
       <c r="E51" t="n">
-        <v>1.146029885322577</v>
+        <v>1.140323569132307</v>
       </c>
       <c r="F51" t="n">
-        <v>1.146609998434266</v>
+        <v>1.140855308286629</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02209247915858113</v>
+        <v>0.02208999245542924</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0262583980514092</v>
+        <v>-0.02407149551522652</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -3210,16 +3210,16 @@
         <v>5.672485518208908</v>
       </c>
       <c r="E52" t="n">
-        <v>1.164503689151217</v>
+        <v>1.158795676807369</v>
       </c>
       <c r="F52" t="n">
-        <v>1.144653830976878</v>
+        <v>1.138902768270085</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0181603741298513</v>
+        <v>0.01816445750446455</v>
       </c>
       <c r="H52" t="n">
-        <v>1.093031345742516</v>
+        <v>1.095155664978969</v>
       </c>
       <c r="I52" t="n">
         <v>-1</v>
@@ -3266,16 +3266,16 @@
         <v>5.63747285479881</v>
       </c>
       <c r="E53" t="n">
-        <v>1.146785852465449</v>
+        <v>1.141113072069623</v>
       </c>
       <c r="F53" t="n">
-        <v>1.143986406210321</v>
+        <v>1.138239837029942</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01780327376817853</v>
+        <v>0.01780864802693181</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1572433413977867</v>
+        <v>0.1613393130874153</v>
       </c>
       <c r="I53" t="n">
         <v>-1</v>
@@ -3322,16 +3322,16 @@
         <v>5.613771107697508</v>
       </c>
       <c r="E54" t="n">
-        <v>1.141619187726321</v>
+        <v>1.135970257521842</v>
       </c>
       <c r="F54" t="n">
-        <v>1.14568891359565</v>
+        <v>1.139948742325326</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01563326937483945</v>
+        <v>0.01563417481235152</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2603246814053702</v>
+        <v>-0.2544736035790314</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -3378,16 +3378,16 @@
         <v>5.610704481843535</v>
       </c>
       <c r="E55" t="n">
-        <v>1.129664945666003</v>
+        <v>1.124019101293683</v>
       </c>
       <c r="F55" t="n">
-        <v>1.144722185336248</v>
+        <v>1.13898771342231</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0160110148582519</v>
+        <v>0.01600751909674719</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.9404300604021204</v>
+        <v>-0.9350988143858677</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3434,16 +3434,16 @@
         <v>5.66083438890224</v>
       </c>
       <c r="E56" t="n">
-        <v>1.148515572526311</v>
+        <v>1.142819284282893</v>
       </c>
       <c r="F56" t="n">
-        <v>1.145026785859405</v>
+        <v>1.139295006196639</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01602292736720544</v>
+        <v>0.01601973968178056</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2177371579456638</v>
+        <v>0.2199959647447871</v>
       </c>
       <c r="I56" t="n">
         <v>-1</v>
@@ -3490,16 +3490,16 @@
         <v>5.694447350642657</v>
       </c>
       <c r="E57" t="n">
-        <v>1.132406083189149</v>
+        <v>1.126675971465722</v>
       </c>
       <c r="F57" t="n">
-        <v>1.143649848269309</v>
+        <v>1.137918995055896</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01585587161762223</v>
+        <v>0.01585349974313543</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.7091231154812994</v>
+        <v>-0.7091824374641557</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3546,16 +3546,16 @@
         <v>5.688985012996693</v>
       </c>
       <c r="E58" t="n">
-        <v>1.145565173593878</v>
+        <v>1.139840558418764</v>
       </c>
       <c r="F58" t="n">
-        <v>1.142584994839778</v>
+        <v>1.136854968053689</v>
       </c>
       <c r="G58" t="n">
-        <v>0.01490132387907618</v>
+        <v>0.01489974807633347</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1999942272434325</v>
+        <v>0.2003785802135508</v>
       </c>
       <c r="I58" t="n">
         <v>-1</v>
@@ -3602,16 +3602,16 @@
         <v>5.703151986226595</v>
       </c>
       <c r="E59" t="n">
-        <v>1.136933783868018</v>
+        <v>1.131194912991799</v>
       </c>
       <c r="F59" t="n">
-        <v>1.142338066146475</v>
+        <v>1.136607756807368</v>
       </c>
       <c r="G59" t="n">
-        <v>0.01495457766889422</v>
+        <v>0.0149531705923957</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3613797994240637</v>
+        <v>-0.3619863614959091</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -3658,16 +3658,16 @@
         <v>5.721221686860314</v>
       </c>
       <c r="E60" t="n">
-        <v>1.126714510603324</v>
+        <v>1.120957456855781</v>
       </c>
       <c r="F60" t="n">
-        <v>1.141183691597189</v>
+        <v>1.135453530278598</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01523652470280289</v>
+        <v>0.01523736444705089</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.9496378784595011</v>
+        <v>-0.9513504433913785</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3714,16 +3714,16 @@
         <v>5.759313628223341</v>
       </c>
       <c r="E61" t="n">
-        <v>1.121820834231199</v>
+        <v>1.116025449972136</v>
       </c>
       <c r="F61" t="n">
-        <v>1.139286196059424</v>
+        <v>1.133554377792955</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01516282490123504</v>
+        <v>0.01516990795864233</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.151854086688159</v>
+        <v>-1.155506537587931</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -3770,16 +3770,16 @@
         <v>5.762993912430139</v>
       </c>
       <c r="E62" t="n">
-        <v>1.129213056466276</v>
+        <v>1.123413968873354</v>
       </c>
       <c r="F62" t="n">
-        <v>1.137606853932245</v>
+        <v>1.131873464837579</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01425424043268824</v>
+        <v>0.01426719667507255</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5888631881583976</v>
+        <v>-0.592933297050896</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -3826,16 +3826,16 @@
         <v>5.759061472992551</v>
       </c>
       <c r="E63" t="n">
-        <v>1.157340794689374</v>
+        <v>1.151545664164793</v>
       </c>
       <c r="F63" t="n">
-        <v>1.137520624354697</v>
+        <v>1.131785015829723</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01412220188238889</v>
+        <v>0.01413212075284925</v>
       </c>
       <c r="H63" t="n">
-        <v>1.403475923920505</v>
+        <v>1.398279046765592</v>
       </c>
       <c r="I63" t="n">
         <v>-1</v>
@@ -3882,16 +3882,16 @@
         <v>5.771809262772875</v>
       </c>
       <c r="E64" t="n">
-        <v>1.151905211385223</v>
+        <v>1.146097253231344</v>
       </c>
       <c r="F64" t="n">
-        <v>1.137809366081225</v>
+        <v>1.132070685804109</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01436445943872254</v>
+        <v>0.01437081816843577</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9813000874923367</v>
+        <v>0.9760451536463793</v>
       </c>
       <c r="I64" t="n">
         <v>-1</v>
@@ -3938,16 +3938,16 @@
         <v>5.807275066409984</v>
       </c>
       <c r="E65" t="n">
-        <v>1.164099059043286</v>
+        <v>1.158255412963136</v>
       </c>
       <c r="F65" t="n">
-        <v>1.138273069681741</v>
+        <v>1.132530076257357</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01507478267880549</v>
+        <v>0.01507247718560414</v>
       </c>
       <c r="H65" t="n">
-        <v>1.713191487520092</v>
+        <v>1.706775627456217</v>
       </c>
       <c r="I65" t="n">
         <v>-1</v>
@@ -3994,16 +3994,16 @@
         <v>5.819841839592116</v>
       </c>
       <c r="E66" t="n">
-        <v>1.167131378336443</v>
+        <v>1.161275086777303</v>
       </c>
       <c r="F66" t="n">
-        <v>1.139857847073019</v>
+        <v>1.134110783149042</v>
       </c>
       <c r="G66" t="n">
-        <v>0.01637111391919556</v>
+        <v>0.01635861732414969</v>
       </c>
       <c r="H66" t="n">
-        <v>1.665954521973309</v>
+        <v>1.660550099681011</v>
       </c>
       <c r="I66" t="n">
         <v>-1</v>
@@ -4050,16 +4050,16 @@
         <v>5.816573506443499</v>
       </c>
       <c r="E67" t="n">
-        <v>1.166829358112802</v>
+        <v>1.160976355356409</v>
       </c>
       <c r="F67" t="n">
-        <v>1.141479761747101</v>
+        <v>1.135728266347706</v>
       </c>
       <c r="G67" t="n">
-        <v>0.01737696388212505</v>
+        <v>0.01735669372464994</v>
       </c>
       <c r="H67" t="n">
-        <v>1.458804687496509</v>
+        <v>1.454660052729164</v>
       </c>
       <c r="I67" t="n">
         <v>-1</v>
@@ -4106,16 +4106,16 @@
         <v>5.833277526334015</v>
       </c>
       <c r="E68" t="n">
-        <v>1.171640771171528</v>
+        <v>1.165770959777824</v>
       </c>
       <c r="F68" t="n">
-        <v>1.143790296205817</v>
+        <v>1.138033437245715</v>
       </c>
       <c r="G68" t="n">
-        <v>0.01818406109637965</v>
+        <v>0.01815457289456872</v>
       </c>
       <c r="H68" t="n">
-        <v>1.531587186057967</v>
+        <v>1.527853213247845</v>
       </c>
       <c r="I68" t="n">
         <v>-1</v>
@@ -4162,16 +4162,16 @@
         <v>5.820731377074562</v>
       </c>
       <c r="E69" t="n">
-        <v>1.18241429142441</v>
+        <v>1.176557104756606</v>
       </c>
       <c r="F69" t="n">
-        <v>1.147593570991108</v>
+        <v>1.141830965350557</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01789323681001069</v>
+        <v>0.01785476193108673</v>
       </c>
       <c r="H69" t="n">
-        <v>1.946026915254459</v>
+        <v>1.944923126955149</v>
       </c>
       <c r="I69" t="n">
         <v>-1</v>
@@ -4218,16 +4218,16 @@
         <v>5.805410967834648</v>
       </c>
       <c r="E70" t="n">
-        <v>1.18242401837799</v>
+        <v>1.176582248071281</v>
       </c>
       <c r="F70" t="n">
-        <v>1.150677872867539</v>
+        <v>1.144910468239198</v>
       </c>
       <c r="G70" t="n">
-        <v>0.018331551071787</v>
+        <v>0.01828822311922893</v>
       </c>
       <c r="H70" t="n">
-        <v>1.731776290294916</v>
+        <v>1.731812851669627</v>
       </c>
       <c r="I70" t="n">
         <v>-1</v>
@@ -4274,16 +4274,16 @@
         <v>5.826346543406457</v>
       </c>
       <c r="E71" t="n">
-        <v>1.180610242538928</v>
+        <v>1.174747405536957</v>
       </c>
       <c r="F71" t="n">
-        <v>1.152406890728356</v>
+        <v>1.146631660059431</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01946578974822397</v>
+        <v>0.01941875944675558</v>
       </c>
       <c r="H71" t="n">
-        <v>1.448867586435582</v>
+        <v>1.447865171542847</v>
       </c>
       <c r="I71" t="n">
         <v>-1</v>
@@ -4330,16 +4330,16 @@
         <v>5.825078484064047</v>
       </c>
       <c r="E72" t="n">
-        <v>1.167284720064792</v>
+        <v>1.16142315906403</v>
       </c>
       <c r="F72" t="n">
-        <v>1.152545942274035</v>
+        <v>1.146763034172264</v>
       </c>
       <c r="G72" t="n">
-        <v>0.01956642264448924</v>
+        <v>0.01951403827582477</v>
       </c>
       <c r="H72" t="n">
-        <v>0.7532689065626484</v>
+        <v>0.7512604354132325</v>
       </c>
       <c r="I72" t="n">
         <v>-1</v>
@@ -4386,16 +4386,16 @@
         <v>5.841206605238948</v>
       </c>
       <c r="E73" t="n">
-        <v>1.198174732751464</v>
+        <v>1.192296942618965</v>
       </c>
       <c r="F73" t="n">
-        <v>1.155115386288336</v>
+        <v>1.149322227699731</v>
       </c>
       <c r="G73" t="n">
-        <v>0.02199380300511742</v>
+        <v>0.02193960780634386</v>
       </c>
       <c r="H73" t="n">
-        <v>1.957794495709034</v>
+        <v>1.958773160330035</v>
       </c>
       <c r="I73" t="n">
         <v>-1</v>
@@ -4442,16 +4442,16 @@
         <v>5.858306968534851</v>
       </c>
       <c r="E74" t="n">
-        <v>1.225319385540698</v>
+        <v>1.219424387945181</v>
       </c>
       <c r="F74" t="n">
-        <v>1.159300396179055</v>
+        <v>1.153494934220898</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02674144036354358</v>
+        <v>0.02668864295463461</v>
       </c>
       <c r="H74" t="n">
-        <v>2.468789581418591</v>
+        <v>2.470318698344832</v>
       </c>
       <c r="I74" t="n">
         <v>-1</v>
@@ -4498,16 +4498,16 @@
         <v>5.85670725340159</v>
       </c>
       <c r="E75" t="n">
-        <v>1.210444553657257</v>
+        <v>1.204551165795903</v>
       </c>
       <c r="F75" t="n">
-        <v>1.163339376578618</v>
+        <v>1.157521537446009</v>
       </c>
       <c r="G75" t="n">
-        <v>0.02809587503466301</v>
+        <v>0.02804792231509403</v>
       </c>
       <c r="H75" t="n">
-        <v>1.676586937424932</v>
+        <v>1.676759790673857</v>
       </c>
       <c r="I75" t="n">
         <v>-1</v>
@@ -4554,16 +4554,16 @@
         <v>5.857164600990844</v>
       </c>
       <c r="E76" t="n">
-        <v>1.191560188552583</v>
+        <v>1.185666340479268</v>
       </c>
       <c r="F76" t="n">
-        <v>1.165491607379931</v>
+        <v>1.159663890255828</v>
       </c>
       <c r="G76" t="n">
-        <v>0.02854563548421038</v>
+        <v>0.02849858090294409</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9132247620506355</v>
+        <v>0.9124121061324201</v>
       </c>
       <c r="I76" t="n">
         <v>-1</v>
@@ -4610,16 +4610,16 @@
         <v>5.952126560232704</v>
       </c>
       <c r="E77" t="n">
-        <v>1.076898709931499</v>
+        <v>1.070909305151374</v>
       </c>
       <c r="F77" t="n">
-        <v>1.162716238717049</v>
+        <v>1.15687555694011</v>
       </c>
       <c r="G77" t="n">
-        <v>0.03409137021669411</v>
+        <v>0.0340779993030861</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.517280128081377</v>
+        <v>-2.522632007359405</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4666,16 +4666,16 @@
         <v>5.954436849899731</v>
       </c>
       <c r="E78" t="n">
-        <v>1.069633591343409</v>
+        <v>1.063641861804252</v>
       </c>
       <c r="F78" t="n">
-        <v>1.158919659604525</v>
+        <v>1.153065622109385</v>
       </c>
       <c r="G78" t="n">
-        <v>0.03984453266982312</v>
+        <v>0.03985295958058151</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.24086122432396</v>
+        <v>-2.243842395803002</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -4722,16 +4722,16 @@
         <v>5.948090365497994</v>
       </c>
       <c r="E79" t="n">
-        <v>1.074282262247248</v>
+        <v>1.06829691894058</v>
       </c>
       <c r="F79" t="n">
-        <v>1.155787083523487</v>
+        <v>1.149920722406824</v>
       </c>
       <c r="G79" t="n">
-        <v>0.04391858408422406</v>
+        <v>0.04394165186036288</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.855816233053739</v>
+        <v>-1.857549728117342</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -4778,16 +4778,16 @@
         <v>5.961515828160556</v>
       </c>
       <c r="E80" t="n">
-        <v>1.054742130057933</v>
+        <v>1.048743277204815</v>
       </c>
       <c r="F80" t="n">
-        <v>1.152188464496217</v>
+        <v>1.146310013424276</v>
       </c>
       <c r="G80" t="n">
-        <v>0.04907237698590421</v>
+        <v>0.04910984833980884</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.985767562599925</v>
+        <v>-1.986704083147669</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -4834,16 +4834,16 @@
         <v>5.98595539627007</v>
       </c>
       <c r="E81" t="n">
-        <v>1.093480554934123</v>
+        <v>1.087457109447669</v>
       </c>
       <c r="F81" t="n">
-        <v>1.150771450531364</v>
+        <v>1.144881596398052</v>
       </c>
       <c r="G81" t="n">
-        <v>0.05038699319613187</v>
+        <v>0.0504346731682618</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.137017550823782</v>
+        <v>-1.138591436070209</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -4890,16 +4890,16 @@
         <v>5.985829728516112</v>
       </c>
       <c r="E82" t="n">
-        <v>1.111074163599475</v>
+        <v>1.105050844567833</v>
       </c>
       <c r="F82" t="n">
-        <v>1.149864505888023</v>
+        <v>1.143963440182776</v>
       </c>
       <c r="G82" t="n">
-        <v>0.05095549753252662</v>
+        <v>0.05100992598830086</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.7612592196511776</v>
+        <v>-0.7628436007507209</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -4946,16 +4946,16 @@
         <v>5.992865390419841</v>
       </c>
       <c r="E83" t="n">
-        <v>1.123431027411388</v>
+        <v>1.117400628653431</v>
       </c>
       <c r="F83" t="n">
-        <v>1.148169017524124</v>
+        <v>1.142256188407208</v>
       </c>
       <c r="G83" t="n">
-        <v>0.05125690306334122</v>
+        <v>0.05131329831772508</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.482627483017576</v>
+        <v>-0.4843882690969328</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -5002,16 +5002,16 @@
         <v>5.962056385069926</v>
       </c>
       <c r="E84" t="n">
-        <v>1.164775494019105</v>
+        <v>1.158776097223564</v>
       </c>
       <c r="F84" t="n">
-        <v>1.148812531655818</v>
+        <v>1.142890130606819</v>
       </c>
       <c r="G84" t="n">
-        <v>0.05138690485937733</v>
+        <v>0.05144140921306883</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3106426122953057</v>
+        <v>0.3088167073912342</v>
       </c>
       <c r="I84" t="n">
         <v>-1</v>
@@ -5058,16 +5058,16 @@
         <v>5.958731556573001</v>
       </c>
       <c r="E85" t="n">
-        <v>1.173219588202269</v>
+        <v>1.167223537058654</v>
       </c>
       <c r="F85" t="n">
-        <v>1.149268558113767</v>
+        <v>1.143338536811595</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0515698469204601</v>
+        <v>0.05162116786331222</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4644386500786536</v>
+        <v>0.4626977892151637</v>
       </c>
       <c r="I85" t="n">
         <v>-1</v>
@@ -5114,16 +5114,16 @@
         <v>5.997396093626087</v>
       </c>
       <c r="E86" t="n">
-        <v>1.168434944511359</v>
+        <v>1.162399986674363</v>
       </c>
       <c r="F86" t="n">
-        <v>1.149333736422513</v>
+        <v>1.143394781806448</v>
       </c>
       <c r="G86" t="n">
-        <v>0.05159442961242068</v>
+        <v>0.05164234810394036</v>
       </c>
       <c r="H86" t="n">
-        <v>0.370218417614754</v>
+        <v>0.3680158932677409</v>
       </c>
       <c r="I86" t="n">
         <v>-1</v>
@@ -5170,16 +5170,16 @@
         <v>5.993538886487244</v>
       </c>
       <c r="E87" t="n">
-        <v>1.214115454287753</v>
+        <v>1.208084377815617</v>
       </c>
       <c r="F87" t="n">
-        <v>1.151698041231261</v>
+        <v>1.145750182929408</v>
       </c>
       <c r="G87" t="n">
-        <v>0.05348708334987745</v>
+        <v>0.05352637522529308</v>
       </c>
       <c r="H87" t="n">
-        <v>1.166962360766589</v>
+        <v>1.164551020386562</v>
       </c>
       <c r="I87" t="n">
         <v>-1</v>
@@ -5226,16 +5226,16 @@
         <v>5.982784867071093</v>
       </c>
       <c r="E88" t="n">
-        <v>1.176528642915369</v>
+        <v>1.170508387815166</v>
       </c>
       <c r="F88" t="n">
-        <v>1.151942434818453</v>
+        <v>1.145987054331275</v>
       </c>
       <c r="G88" t="n">
-        <v>0.05359406161049111</v>
+        <v>0.0536300186427189</v>
       </c>
       <c r="H88" t="n">
-        <v>0.4587487374180239</v>
+        <v>0.4572314928184245</v>
       </c>
       <c r="I88" t="n">
         <v>-1</v>
@@ -5282,16 +5282,16 @@
         <v>5.983188051122531</v>
       </c>
       <c r="E89" t="n">
-        <v>1.162839098401851</v>
+        <v>1.156818437592451</v>
       </c>
       <c r="F89" t="n">
-        <v>1.150963675167325</v>
+        <v>1.145000120973068</v>
       </c>
       <c r="G89" t="n">
-        <v>0.05318546951417199</v>
+        <v>0.05321787848775986</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2232832264715047</v>
+        <v>0.2220741779870281</v>
       </c>
       <c r="I89" t="n">
         <v>-1</v>
@@ -5338,16 +5338,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="E90" t="n">
-        <v>1.17188237582652</v>
+        <v>1.165885519684128</v>
       </c>
       <c r="F90" t="n">
-        <v>1.150436593039751</v>
+        <v>1.14446528455371</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0529087952654414</v>
+        <v>0.05293678322767557</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4053349292717108</v>
+        <v>0.4046380196222276</v>
       </c>
       <c r="I90" t="n">
         <v>-1</v>
@@ -5394,16 +5394,16 @@
         <v>5.962750867995942</v>
       </c>
       <c r="E91" t="n">
-        <v>1.182481690257254</v>
+        <v>1.176481594629234</v>
       </c>
       <c r="F91" t="n">
-        <v>1.150530165425668</v>
+        <v>1.144551994008324</v>
       </c>
       <c r="G91" t="n">
-        <v>0.05296659112274621</v>
+        <v>0.05299038852292588</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6032392146502528</v>
+        <v>0.602554567175813</v>
       </c>
       <c r="I91" t="n">
         <v>-1</v>
@@ -5450,16 +5450,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="E92" t="n">
-        <v>1.166883706266199</v>
+        <v>1.160886850123807</v>
       </c>
       <c r="F92" t="n">
-        <v>1.150510114735738</v>
+        <v>1.144525178561313</v>
       </c>
       <c r="G92" t="n">
-        <v>0.05295999030270203</v>
+        <v>0.0529815365918388</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3091690809774454</v>
+        <v>0.3088183660761216</v>
       </c>
       <c r="I92" t="n">
         <v>-1</v>
@@ -5506,16 +5506,16 @@
         <v>5.94735954974672</v>
       </c>
       <c r="E93" t="n">
-        <v>1.15628363653086</v>
+        <v>1.150299028617049</v>
       </c>
       <c r="F93" t="n">
-        <v>1.148415559924708</v>
+        <v>1.142425282861217</v>
       </c>
       <c r="G93" t="n">
-        <v>0.05179114201370383</v>
+        <v>0.05180775487434046</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1519193495302854</v>
+        <v>0.1519800611883205</v>
       </c>
       <c r="I93" t="n">
         <v>-1</v>
@@ -5562,16 +5562,16 @@
         <v>5.962673683416126</v>
       </c>
       <c r="E94" t="n">
-        <v>1.143245871391414</v>
+        <v>1.137245853431382</v>
       </c>
       <c r="F94" t="n">
-        <v>1.144311884217244</v>
+        <v>1.138316356135527</v>
       </c>
       <c r="G94" t="n">
-        <v>0.04852554922789332</v>
+        <v>0.04853491665856365</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.02196807337148494</v>
+        <v>-0.02205634165761407</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -5618,16 +5618,16 @@
         <v>5.962545055387006</v>
       </c>
       <c r="E95" t="n">
-        <v>1.132762834859047</v>
+        <v>1.126762946332642</v>
       </c>
       <c r="F95" t="n">
-        <v>1.140427798277333</v>
+        <v>1.134426945162364</v>
       </c>
       <c r="G95" t="n">
-        <v>0.04599655463730506</v>
+        <v>0.04599828685539024</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.1666421208876613</v>
+        <v>-0.1666148753282085</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -5674,16 +5674,16 @@
         <v>5.965882922901972</v>
       </c>
       <c r="E96" t="n">
-        <v>1.138128438368819</v>
+        <v>1.132125191069806</v>
       </c>
       <c r="F96" t="n">
-        <v>1.137756210768145</v>
+        <v>1.131749887691891</v>
       </c>
       <c r="G96" t="n">
-        <v>0.04439416501244557</v>
+        <v>0.04438912573358054</v>
       </c>
       <c r="H96" t="n">
-        <v>0.008384606413237619</v>
+        <v>0.00845484950903432</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -5730,16 +5730,16 @@
         <v>5.940468433706842</v>
       </c>
       <c r="E97" t="n">
-        <v>1.141516871338433</v>
+        <v>1.13553919769978</v>
       </c>
       <c r="F97" t="n">
-        <v>1.140987118838491</v>
+        <v>1.134981382319311</v>
       </c>
       <c r="G97" t="n">
-        <v>0.04201987479411851</v>
+        <v>0.04201592832070787</v>
       </c>
       <c r="H97" t="n">
-        <v>0.01260718892040579</v>
+        <v>0.01327628360870214</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -5786,16 +5786,16 @@
         <v>5.929975570597685</v>
       </c>
       <c r="E98" t="n">
-        <v>1.209683322636755</v>
+        <v>1.203716207578103</v>
       </c>
       <c r="F98" t="n">
-        <v>1.147989605403159</v>
+        <v>1.141985099608004</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0411639046311005</v>
+        <v>0.04116432686530905</v>
       </c>
       <c r="H98" t="n">
-        <v>1.498733363282178</v>
+        <v>1.499626318974815</v>
       </c>
       <c r="I98" t="n">
         <v>-1</v>
@@ -5842,16 +5842,16 @@
         <v>5.890632658072621</v>
       </c>
       <c r="E99" t="n">
-        <v>1.230676879989183</v>
+        <v>1.224749354248056</v>
       </c>
       <c r="F99" t="n">
-        <v>1.155809336290255</v>
+        <v>1.149807721373378</v>
       </c>
       <c r="G99" t="n">
-        <v>0.04127974077177707</v>
+        <v>0.04128950419045137</v>
       </c>
       <c r="H99" t="n">
-        <v>1.813663126249919</v>
+        <v>1.81502864575471</v>
       </c>
       <c r="I99" t="n">
         <v>-1</v>
@@ -5898,16 +5898,16 @@
         <v>5.882697390434339</v>
       </c>
       <c r="E100" t="n">
-        <v>1.199410655546822</v>
+        <v>1.193491114771983</v>
       </c>
       <c r="F100" t="n">
-        <v>1.1630427625647</v>
+        <v>1.157045113251736</v>
       </c>
       <c r="G100" t="n">
-        <v>0.03480499715895827</v>
+        <v>0.0348215451524446</v>
       </c>
       <c r="H100" t="n">
-        <v>1.044904351407538</v>
+        <v>1.046650898479403</v>
       </c>
       <c r="I100" t="n">
         <v>-1</v>
@@ -5954,16 +5954,16 @@
         <v>5.918807384063352</v>
       </c>
       <c r="E101" t="n">
-        <v>1.193028828113042</v>
+        <v>1.187072951187373</v>
       </c>
       <c r="F101" t="n">
-        <v>1.168020176223646</v>
+        <v>1.162025905338721</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03127226716525897</v>
+        <v>0.03128920707700784</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7997070297857722</v>
+        <v>0.8005011372454208</v>
       </c>
       <c r="I101" t="n">
         <v>-1</v>
@@ -6010,16 +6010,16 @@
         <v>5.908924968232186</v>
       </c>
       <c r="E102" t="n">
-        <v>1.136011879133064</v>
+        <v>1.130065946516881</v>
       </c>
       <c r="F102" t="n">
-        <v>1.169267062000325</v>
+        <v>1.163276660436174</v>
       </c>
       <c r="G102" t="n">
-        <v>0.02931833217190074</v>
+        <v>0.02933048419793497</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.134279490125075</v>
+        <v>-1.132293408290572</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -6066,16 +6066,16 @@
         <v>5.895256457589491</v>
       </c>
       <c r="E103" t="n">
-        <v>1.16281094195557</v>
+        <v>1.15687876345603</v>
       </c>
       <c r="F103" t="n">
-        <v>1.171236057727534</v>
+        <v>1.165250567176303</v>
       </c>
       <c r="G103" t="n">
-        <v>0.02733315700102877</v>
+        <v>0.0273415679291707</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.308237931375709</v>
+        <v>-0.3061932564350664</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -6122,16 +6122,16 @@
         <v>5.897867925179888</v>
       </c>
       <c r="E104" t="n">
-        <v>1.158801129902608</v>
+        <v>1.152866323579834</v>
       </c>
       <c r="F104" t="n">
-        <v>1.17093733952171</v>
+        <v>1.164955078494117</v>
       </c>
       <c r="G104" t="n">
-        <v>0.02743991700200881</v>
+        <v>0.02744695348518994</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.4422830294352884</v>
+        <v>-0.4404406820890471</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -6178,16 +6178,16 @@
         <v>5.875997591000409</v>
       </c>
       <c r="E105" t="n">
-        <v>1.136264028561349</v>
+        <v>1.130351229546846</v>
       </c>
       <c r="F105" t="n">
-        <v>1.169089561539664</v>
+        <v>1.163111463118526</v>
       </c>
       <c r="G105" t="n">
-        <v>0.02850187068741539</v>
+        <v>0.028504544385053</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.151697491660009</v>
+        <v>-1.149298621621159</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -6234,16 +6234,16 @@
         <v>5.879890291127706</v>
       </c>
       <c r="E106" t="n">
-        <v>1.155465835832535</v>
+        <v>1.149549119737889</v>
       </c>
       <c r="F106" t="n">
-        <v>1.168441106105722</v>
+        <v>1.162468919771703</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02866461555247627</v>
+        <v>0.02866581099643415</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.4526580951149872</v>
+        <v>-0.4507041519048759</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -6290,16 +6290,16 @@
         <v>5.885214726902118</v>
       </c>
       <c r="E107" t="n">
-        <v>1.153253344017569</v>
+        <v>1.147331270140163</v>
       </c>
       <c r="F107" t="n">
-        <v>1.165398000592213</v>
+        <v>1.15943126438793</v>
       </c>
       <c r="G107" t="n">
-        <v>0.02672556013171084</v>
+        <v>0.02673129163869092</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.454421030458922</v>
+        <v>-0.4526528089743906</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -6346,16 +6346,16 @@
         <v>5.911744720499765</v>
       </c>
       <c r="E108" t="n">
-        <v>1.169222558854963</v>
+        <v>1.16327378882638</v>
       </c>
       <c r="F108" t="n">
-        <v>1.165032696389193</v>
+        <v>1.159069534438491</v>
       </c>
       <c r="G108" t="n">
-        <v>0.02661511524133806</v>
+        <v>0.02662223295262581</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1574241714821622</v>
+        <v>0.1579226804667478</v>
       </c>
       <c r="I108" t="n">
         <v>-1</v>
@@ -6402,16 +6402,16 @@
         <v>5.9222484364193</v>
       </c>
       <c r="E109" t="n">
-        <v>1.137769752448219</v>
+        <v>1.131810412918853</v>
       </c>
       <c r="F109" t="n">
-        <v>1.163779229091511</v>
+        <v>1.157819133204811</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02730524863923257</v>
+        <v>0.02731188739108418</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.9525449479306901</v>
+        <v>-0.9522857176999211</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -6458,16 +6458,16 @@
         <v>5.896576801564275</v>
       </c>
       <c r="E110" t="n">
-        <v>1.142566149313986</v>
+        <v>1.136632642201146</v>
       </c>
       <c r="F110" t="n">
-        <v>1.162313417765884</v>
+        <v>1.156356489330661</v>
       </c>
       <c r="G110" t="n">
-        <v>0.02763228200907108</v>
+        <v>0.0276385113969667</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.7146448652129203</v>
+        <v>-0.7136363766566687</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -6514,16 +6514,16 @@
         <v>5.908164453268487</v>
       </c>
       <c r="E111" t="n">
-        <v>1.163441009886336</v>
+        <v>1.157495842548228</v>
       </c>
       <c r="F111" t="n">
-        <v>1.161361383747339</v>
+        <v>1.155407201726611</v>
       </c>
       <c r="G111" t="n">
-        <v>0.02722586042795039</v>
+        <v>0.02723399023273421</v>
       </c>
       <c r="H111" t="n">
-        <v>0.07638422096890977</v>
+        <v>0.07669242750578384</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -6570,16 +6570,16 @@
         <v>5.857018429609569</v>
       </c>
       <c r="E112" t="n">
-        <v>1.189957038717434</v>
+        <v>1.184063337730973</v>
       </c>
       <c r="F112" t="n">
-        <v>1.1625150503699</v>
+        <v>1.15656602610697</v>
       </c>
       <c r="G112" t="n">
-        <v>0.02795136617360552</v>
+        <v>0.02796276129086676</v>
       </c>
       <c r="H112" t="n">
-        <v>0.9817762815989773</v>
+        <v>0.9833546600773144</v>
       </c>
       <c r="I112" t="n">
         <v>-1</v>
@@ -6626,16 +6626,16 @@
         <v>5.846814441141912</v>
       </c>
       <c r="E113" t="n">
-        <v>1.155047448171035</v>
+        <v>1.149164015080709</v>
       </c>
       <c r="F113" t="n">
-        <v>1.162453240951909</v>
+        <v>1.156509275430153</v>
       </c>
       <c r="G113" t="n">
-        <v>0.02796723336949554</v>
+        <v>0.02797729761798207</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.2648024809258331</v>
+        <v>-0.2625435969456406</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -6682,16 +6682,16 @@
         <v>5.84438466839932</v>
       </c>
       <c r="E114" t="n">
-        <v>1.151556870229493</v>
+        <v>1.145675882129597</v>
       </c>
       <c r="F114" t="n">
-        <v>1.162868790893813</v>
+        <v>1.156930776865063</v>
       </c>
       <c r="G114" t="n">
-        <v>0.02772753801105472</v>
+        <v>0.02773425031693609</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.4079670059350384</v>
+        <v>-0.4058121134283493</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -6738,16 +6738,16 @@
         <v>5.839798253712797</v>
       </c>
       <c r="E115" t="n">
-        <v>1.138289582239383</v>
+        <v>1.132413209278928</v>
       </c>
       <c r="F115" t="n">
-        <v>1.16314512826283</v>
+        <v>1.157213290012378</v>
       </c>
       <c r="G115" t="n">
-        <v>0.02743773101465209</v>
+        <v>0.02743796929338175</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.9058892665058047</v>
+        <v>-0.9038599201082863</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -6794,16 +6794,16 @@
         <v>5.821239574678188</v>
       </c>
       <c r="E116" t="n">
-        <v>1.134906289646365</v>
+        <v>1.12904859159811</v>
       </c>
       <c r="F116" t="n">
-        <v>1.162984020826707</v>
+        <v>1.157059460038793</v>
       </c>
       <c r="G116" t="n">
-        <v>0.02760132596209426</v>
+        <v>0.02759420732017341</v>
       </c>
       <c r="H116" t="n">
-        <v>-1.017260229414436</v>
+        <v>-1.015099586506513</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -6850,16 +6850,16 @@
         <v>5.868307706223366</v>
       </c>
       <c r="E117" t="n">
-        <v>1.114144180904709</v>
+        <v>1.108239119936798</v>
       </c>
       <c r="F117" t="n">
-        <v>1.161615386305021</v>
+        <v>1.155694456150644</v>
       </c>
       <c r="G117" t="n">
-        <v>0.02934536540994907</v>
+        <v>0.02933509168500632</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.617673003458916</v>
+        <v>-1.61769858173314</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -6906,16 +6906,16 @@
         <v>5.878771645975505</v>
       </c>
       <c r="E118" t="n">
-        <v>1.132650226817892</v>
+        <v>1.126734636374484</v>
       </c>
       <c r="F118" t="n">
-        <v>1.157763731514078</v>
+        <v>1.151845377590463</v>
       </c>
       <c r="G118" t="n">
-        <v>0.02771433983582536</v>
+        <v>0.02770775961545112</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.9061556163687622</v>
+        <v>-0.906271079455169</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -6950,28 +6950,28 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>195.8800048828125</v>
+        <v>197.25</v>
       </c>
       <c r="B119" t="n">
-        <v>361.875</v>
+        <v>359.2000122070312</v>
       </c>
       <c r="C119" t="n">
-        <v>5.277502251761687</v>
+        <v>5.284471959725984</v>
       </c>
       <c r="D119" t="n">
-        <v>5.89129884832726</v>
+        <v>5.883879370411984</v>
       </c>
       <c r="E119" t="n">
-        <v>1.102507562190543</v>
+        <v>1.108814511404454</v>
       </c>
       <c r="F119" t="n">
-        <v>1.151355265624146</v>
+        <v>1.146048635448283</v>
       </c>
       <c r="G119" t="n">
-        <v>0.02461188880953677</v>
+        <v>0.0234535376730178</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.984719816167663</v>
+        <v>-1.587569626507362</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -6986,22 +6986,22 @@
         <v>-1</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.02104048944040526</v>
+        <v>-0.01419359483167137</v>
       </c>
       <c r="N119" t="n">
-        <v>0.01260599643049276</v>
+        <v>0.005120791098434774</v>
       </c>
       <c r="O119" t="n">
-        <v>-0.02111985451977034</v>
+        <v>-0.01427295991103645</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.01260599643049276</v>
+        <v>-0.005120791098434774</v>
       </c>
       <c r="Q119" t="n">
-        <v>-0.03372585095026311</v>
+        <v>-0.01939375100947123</v>
       </c>
       <c r="R119" t="n">
-        <v>192.8044081629949</v>
+        <v>195.6641473472986</v>
       </c>
     </row>
   </sheetData>
